--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -30,6 +30,12 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Valor Despesa Empenhada</t>
+  </si>
+  <si>
+    <t>Valor Despesa Liquidada</t>
+  </si>
+  <si>
     <t>Valor Pago Financeiro</t>
   </si>
   <si>
@@ -204,6 +210,12 @@
     <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
   </si>
   <si>
+    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
     <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
   </si>
   <si>
@@ -228,9 +240,6 @@
     <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
   </si>
   <si>
-    <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
-  </si>
-  <si>
     <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
   </si>
   <si>
@@ -244,9 +253,6 @@
   </si>
   <si>
     <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
   </si>
   <si>
     <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
@@ -275,7 +281,6 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -628,20 +633,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="4" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -654,17 +659,23 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>2024</v>
       </c>
@@ -672,22 +683,28 @@
         <v>1071</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="6">
+        <v>39892772.32</v>
+      </c>
+      <c r="E2" s="6">
+        <v>35166360.520000003</v>
+      </c>
+      <c r="F2" s="6">
         <v>34432753.310000002</v>
       </c>
-      <c r="E2" s="6">
+      <c r="G2" s="6">
         <v>630087.11</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>7450507.5999999996</v>
       </c>
-      <c r="G2" s="7">
+      <c r="I2" s="7">
         <v>8080594.71</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2024</v>
       </c>
@@ -695,22 +712,28 @@
         <v>1081</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
+        <v>1176383140.29</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1169049193.7</v>
+      </c>
+      <c r="F3" s="6">
         <v>1101390201.9200001</v>
       </c>
-      <c r="E3" s="6">
+      <c r="G3" s="6">
         <v>269694170.11000001</v>
       </c>
-      <c r="F3" s="6">
+      <c r="H3" s="6">
         <v>1347728.41</v>
       </c>
-      <c r="G3" s="7">
+      <c r="I3" s="7">
         <v>271041898.51999998</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>2024</v>
       </c>
@@ -718,22 +741,28 @@
         <v>1101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6">
+        <v>16775084.75</v>
+      </c>
+      <c r="E4" s="6">
+        <v>16686029.560000001</v>
+      </c>
+      <c r="F4" s="6">
         <v>16501107.08</v>
       </c>
-      <c r="E4" s="6">
+      <c r="G4" s="6">
         <v>0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="H4" s="6">
         <v>35612.89</v>
       </c>
-      <c r="G4" s="7">
+      <c r="I4" s="7">
         <v>35612.89</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2024</v>
       </c>
@@ -741,22 +770,28 @@
         <v>1191</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
+        <v>1774005537.77</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1675743095.8699999</v>
+      </c>
+      <c r="F5" s="6">
         <v>1655219211.46</v>
       </c>
-      <c r="E5" s="6">
+      <c r="G5" s="6">
         <v>9452783.4299999997</v>
       </c>
-      <c r="F5" s="6">
+      <c r="H5" s="6">
         <v>44016084.479999997</v>
       </c>
-      <c r="G5" s="7">
+      <c r="I5" s="7">
         <v>53468867.909999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2024</v>
       </c>
@@ -764,22 +799,28 @@
         <v>1221</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6">
+        <v>73450042.359999999</v>
+      </c>
+      <c r="E6" s="6">
+        <v>68755382.680000007</v>
+      </c>
+      <c r="F6" s="6">
         <v>67360741.430000007</v>
       </c>
-      <c r="E6" s="6">
+      <c r="G6" s="6">
         <v>20159858.670000002</v>
       </c>
-      <c r="F6" s="6">
+      <c r="H6" s="6">
         <v>2093275.95</v>
       </c>
-      <c r="G6" s="7">
+      <c r="I6" s="7">
         <v>22253134.620000001</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2024</v>
       </c>
@@ -787,22 +828,28 @@
         <v>1231</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6">
+        <v>144310208.36000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>121768607.78</v>
+      </c>
+      <c r="F7" s="6">
         <v>115667927.76000001</v>
       </c>
-      <c r="E7" s="6">
+      <c r="G7" s="6">
         <v>16655601.210000001</v>
       </c>
-      <c r="F7" s="6">
+      <c r="H7" s="6">
         <v>13370006.41</v>
       </c>
-      <c r="G7" s="7">
+      <c r="I7" s="7">
         <v>30025607.620000001</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2024</v>
       </c>
@@ -810,22 +857,28 @@
         <v>1251</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
+        <v>14358949915.030001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>14172994593.1</v>
+      </c>
+      <c r="F8" s="6">
         <v>14136708514.629999</v>
       </c>
-      <c r="E8" s="6">
+      <c r="G8" s="6">
         <v>25047110.829999998</v>
       </c>
-      <c r="F8" s="6">
+      <c r="H8" s="6">
         <v>200233686.02000001</v>
       </c>
-      <c r="G8" s="7">
+      <c r="I8" s="7">
         <v>225280796.84999999</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2024</v>
       </c>
@@ -833,22 +886,28 @@
         <v>1261</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6">
+        <v>19265871510.98</v>
+      </c>
+      <c r="E9" s="6">
+        <v>18803285393.110001</v>
+      </c>
+      <c r="F9" s="6">
         <v>18714498875.099998</v>
       </c>
-      <c r="E9" s="6">
+      <c r="G9" s="6">
         <v>270741595.99000001</v>
       </c>
-      <c r="F9" s="6">
+      <c r="H9" s="6">
         <v>353672915.63999999</v>
       </c>
-      <c r="G9" s="7">
+      <c r="I9" s="7">
         <v>624414511.63</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2024</v>
       </c>
@@ -856,22 +915,28 @@
         <v>1271</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6">
+        <v>278574229.64999998</v>
+      </c>
+      <c r="E10" s="6">
+        <v>275244209.69</v>
+      </c>
+      <c r="F10" s="6">
         <v>272306597.25999999</v>
       </c>
-      <c r="E10" s="6">
+      <c r="G10" s="6">
         <v>2848477.47</v>
       </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>1058475.57</v>
       </c>
-      <c r="G10" s="7">
+      <c r="I10" s="7">
         <v>3906953.04</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>2024</v>
       </c>
@@ -879,22 +944,28 @@
         <v>1301</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="6">
+        <v>739415330.30999994</v>
+      </c>
+      <c r="E11" s="6">
+        <v>535038118.5</v>
+      </c>
+      <c r="F11" s="6">
         <v>520804921.24000001</v>
       </c>
-      <c r="E11" s="6">
+      <c r="G11" s="6">
         <v>79602772.469999999</v>
       </c>
-      <c r="F11" s="6">
+      <c r="H11" s="6">
         <v>79301096.689999998</v>
       </c>
-      <c r="G11" s="7">
+      <c r="I11" s="7">
         <v>158903869.16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2024</v>
       </c>
@@ -902,22 +973,28 @@
         <v>1371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6">
+        <v>184730264.22999999</v>
+      </c>
+      <c r="E12" s="6">
+        <v>174620059.84999999</v>
+      </c>
+      <c r="F12" s="6">
         <v>171768182.38999999</v>
       </c>
-      <c r="E12" s="6">
+      <c r="G12" s="6">
         <v>16148951.810000001</v>
       </c>
-      <c r="F12" s="6">
+      <c r="H12" s="6">
         <v>3698488.6</v>
       </c>
-      <c r="G12" s="7">
+      <c r="I12" s="7">
         <v>19847440.41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>2024</v>
       </c>
@@ -925,22 +1002,28 @@
         <v>1401</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6">
+        <v>1689247203.3900001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1633624349.8599999</v>
+      </c>
+      <c r="F13" s="6">
         <v>1628884534.1500001</v>
       </c>
-      <c r="E13" s="6">
+      <c r="G13" s="6">
         <v>6962587.3899999997</v>
       </c>
-      <c r="F13" s="6">
+      <c r="H13" s="6">
         <v>71853078.969999999</v>
       </c>
-      <c r="G13" s="7">
+      <c r="I13" s="7">
         <v>78815666.359999999</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2024</v>
       </c>
@@ -948,22 +1031,28 @@
         <v>1451</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6">
+        <v>4151305223.1199999</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4013226715.0500002</v>
+      </c>
+      <c r="F14" s="6">
         <v>3984233963.5300002</v>
       </c>
-      <c r="E14" s="6">
+      <c r="G14" s="6">
         <v>16641871.41</v>
       </c>
-      <c r="F14" s="6">
+      <c r="H14" s="6">
         <v>126747618.81</v>
       </c>
-      <c r="G14" s="7">
+      <c r="I14" s="7">
         <v>143389490.22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2024</v>
       </c>
@@ -971,22 +1060,28 @@
         <v>1481</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6">
+        <v>192351891.56999999</v>
+      </c>
+      <c r="E15" s="6">
+        <v>161820266.28</v>
+      </c>
+      <c r="F15" s="6">
         <v>151442671.16</v>
       </c>
-      <c r="E15" s="6">
+      <c r="G15" s="6">
         <v>69047832.109999999</v>
       </c>
-      <c r="F15" s="6">
+      <c r="H15" s="6">
         <v>5228463.57</v>
       </c>
-      <c r="G15" s="7">
+      <c r="I15" s="7">
         <v>74276295.680000007</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2024</v>
       </c>
@@ -994,22 +1089,28 @@
         <v>1491</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6">
+        <v>936918721.66999996</v>
+      </c>
+      <c r="E16" s="6">
+        <v>903588865.71000004</v>
+      </c>
+      <c r="F16" s="6">
         <v>899254287.63999999</v>
       </c>
-      <c r="E16" s="6">
+      <c r="G16" s="6">
         <v>2218245.96</v>
       </c>
-      <c r="F16" s="6">
+      <c r="H16" s="6">
         <v>40834360.640000001</v>
       </c>
-      <c r="G16" s="7">
+      <c r="I16" s="7">
         <v>43052606.600000001</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>2024</v>
       </c>
@@ -1017,22 +1118,28 @@
         <v>1501</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
+        <v>855546794.05999994</v>
+      </c>
+      <c r="E17" s="6">
+        <v>760671962.16999996</v>
+      </c>
+      <c r="F17" s="6">
         <v>719982759.67999995</v>
       </c>
-      <c r="E17" s="6">
+      <c r="G17" s="6">
         <v>10865754.289999999</v>
       </c>
-      <c r="F17" s="6">
+      <c r="H17" s="6">
         <v>34522196.210000001</v>
       </c>
-      <c r="G17" s="7">
+      <c r="I17" s="7">
         <v>45387950.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2024</v>
       </c>
@@ -1040,22 +1147,28 @@
         <v>1511</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
+        <v>2971107807.8499999</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2911787285.4699998</v>
+      </c>
+      <c r="F18" s="6">
         <v>2882948197.5799999</v>
       </c>
-      <c r="E18" s="6">
+      <c r="G18" s="6">
         <v>6144267.3899999997</v>
       </c>
-      <c r="F18" s="6">
+      <c r="H18" s="6">
         <v>64134975.090000004</v>
       </c>
-      <c r="G18" s="7">
+      <c r="I18" s="7">
         <v>70279242.480000004</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>2024</v>
       </c>
@@ -1063,22 +1176,28 @@
         <v>1521</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="6">
+        <v>67525357.700000003</v>
+      </c>
+      <c r="E19" s="6">
+        <v>66249891.549999997</v>
+      </c>
+      <c r="F19" s="6">
         <v>66020996.240000002</v>
       </c>
-      <c r="E19" s="6">
+      <c r="G19" s="6">
         <v>96745.82</v>
       </c>
-      <c r="F19" s="6">
+      <c r="H19" s="6">
         <v>487607.59</v>
       </c>
-      <c r="G19" s="7">
+      <c r="I19" s="7">
         <v>584353.41</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>2024</v>
       </c>
@@ -1086,22 +1205,28 @@
         <v>1541</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6">
+        <v>21259443.359999999</v>
+      </c>
+      <c r="E20" s="6">
+        <v>20594781.940000001</v>
+      </c>
+      <c r="F20" s="6">
         <v>20198969.09</v>
       </c>
-      <c r="E20" s="6">
+      <c r="G20" s="6">
         <v>11884.85</v>
       </c>
-      <c r="F20" s="6">
+      <c r="H20" s="6">
         <v>215304.71</v>
       </c>
-      <c r="G20" s="7">
+      <c r="I20" s="7">
         <v>227189.56</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>2024</v>
       </c>
@@ -1109,22 +1234,28 @@
         <v>1631</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
+        <v>9422516.7100000009</v>
+      </c>
+      <c r="E21" s="6">
+        <v>9269804.5999999996</v>
+      </c>
+      <c r="F21" s="6">
         <v>9157892.9600000009</v>
       </c>
-      <c r="E21" s="6">
+      <c r="G21" s="6">
         <v>7873.12</v>
       </c>
-      <c r="F21" s="6">
+      <c r="H21" s="6">
         <v>3228098.93</v>
       </c>
-      <c r="G21" s="7">
+      <c r="I21" s="7">
         <v>3235972.05</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>2024</v>
       </c>
@@ -1132,22 +1263,28 @@
         <v>1711</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
+        <v>145415971.84</v>
+      </c>
+      <c r="E22" s="6">
+        <v>57212986.340000004</v>
+      </c>
+      <c r="F22" s="6">
         <v>54811118.270000003</v>
       </c>
-      <c r="E22" s="6">
+      <c r="G22" s="6">
         <v>13711.91</v>
       </c>
-      <c r="F22" s="6">
+      <c r="H22" s="6">
         <v>45385504.039999999</v>
       </c>
-      <c r="G22" s="7">
+      <c r="I22" s="7">
         <v>45399215.950000003</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>2024</v>
       </c>
@@ -1155,22 +1292,28 @@
         <v>1721</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
+        <v>11376822.58</v>
+      </c>
+      <c r="E23" s="6">
+        <v>10825343.529999999</v>
+      </c>
+      <c r="F23" s="6">
         <v>10646102.960000001</v>
       </c>
-      <c r="E23" s="6">
+      <c r="G23" s="6">
         <v>256630.64</v>
       </c>
-      <c r="F23" s="6">
+      <c r="H23" s="6">
         <v>226579.48</v>
       </c>
-      <c r="G23" s="7">
+      <c r="I23" s="7">
         <v>483210.12</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>2024</v>
       </c>
@@ -1178,22 +1321,28 @@
         <v>1911</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6">
+        <v>1542024334.1800001</v>
+      </c>
+      <c r="E24" s="6">
         <v>1424388867.28</v>
       </c>
-      <c r="E24" s="6">
+      <c r="F24" s="6">
+        <v>1424388867.28</v>
+      </c>
+      <c r="G24" s="6">
         <v>23280.48</v>
       </c>
-      <c r="F24" s="6">
+      <c r="H24" s="6">
         <v>58649930.030000001</v>
       </c>
-      <c r="G24" s="7">
+      <c r="I24" s="7">
         <v>58673210.509999998</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>2024</v>
       </c>
@@ -1201,22 +1350,28 @@
         <v>1915</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
+        <v>77370454.079999998</v>
+      </c>
+      <c r="E25" s="6">
         <v>77346508.569999993</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F25" s="6">
+        <v>77346508.569999993</v>
+      </c>
+      <c r="G25" s="6">
         <v>0</v>
       </c>
-      <c r="F25" s="6">
+      <c r="H25" s="6">
         <v>259334068.69999999</v>
       </c>
-      <c r="G25" s="7">
+      <c r="I25" s="7">
         <v>259334068.69999999</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>2024</v>
       </c>
@@ -1224,22 +1379,28 @@
         <v>1916</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="6">
+        <v>3797673691.6900001</v>
+      </c>
+      <c r="E26" s="6">
+        <v>3797673691.6900001</v>
+      </c>
+      <c r="F26" s="6">
         <v>3525271258.0100002</v>
       </c>
-      <c r="E26" s="6">
+      <c r="G26" s="6">
         <v>158424713.63999999</v>
       </c>
-      <c r="F26" s="6">
+      <c r="H26" s="6">
         <v>0</v>
       </c>
-      <c r="G26" s="7">
+      <c r="I26" s="7">
         <v>158424713.63999999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>2024</v>
       </c>
@@ -1247,22 +1408,28 @@
         <v>1941</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6">
+        <v>198068287.50999999</v>
+      </c>
+      <c r="E27" s="6">
+        <v>195102654.49000001</v>
+      </c>
+      <c r="F27" s="6">
         <v>195045661.81</v>
       </c>
-      <c r="E27" s="6">
+      <c r="G27" s="6">
         <v>0</v>
       </c>
-      <c r="F27" s="6">
+      <c r="H27" s="6">
         <v>306318.7</v>
       </c>
-      <c r="G27" s="7">
+      <c r="I27" s="7">
         <v>306318.7</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>2024</v>
       </c>
@@ -1270,22 +1437,28 @@
         <v>2011</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D28" s="6">
+        <v>1725474955.8</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1598962422.8800001</v>
+      </c>
+      <c r="F28" s="6">
         <v>1555299505.74</v>
       </c>
-      <c r="E28" s="6">
+      <c r="G28" s="6">
         <v>1217572.7</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>166587616.34999999</v>
       </c>
-      <c r="G28" s="7">
+      <c r="I28" s="7">
         <v>167805189.05000001</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>2024</v>
       </c>
@@ -1293,22 +1466,28 @@
         <v>2041</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6">
+        <v>2753285.11</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2718960.43</v>
+      </c>
+      <c r="F29" s="6">
         <v>2712294.25</v>
       </c>
-      <c r="E29" s="6">
+      <c r="G29" s="6">
         <v>0</v>
       </c>
-      <c r="F29" s="6">
+      <c r="H29" s="6">
         <v>52615.45</v>
       </c>
-      <c r="G29" s="7">
+      <c r="I29" s="7">
         <v>52615.45</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>2024</v>
       </c>
@@ -1316,22 +1495,28 @@
         <v>2061</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6">
+        <v>69147295.900000006</v>
+      </c>
+      <c r="E30" s="6">
+        <v>66097932.409999996</v>
+      </c>
+      <c r="F30" s="6">
         <v>64809217.450000003</v>
       </c>
-      <c r="E30" s="6">
+      <c r="G30" s="6">
         <v>10992.51</v>
       </c>
-      <c r="F30" s="6">
+      <c r="H30" s="6">
         <v>2944724.82</v>
       </c>
-      <c r="G30" s="7">
+      <c r="I30" s="7">
         <v>2955717.33</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2024</v>
       </c>
@@ -1339,22 +1524,28 @@
         <v>2071</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="6">
+        <v>533594583.23000002</v>
+      </c>
+      <c r="E31" s="6">
+        <v>523602791.54000002</v>
+      </c>
+      <c r="F31" s="6">
         <v>524266165.17000002</v>
       </c>
-      <c r="E31" s="6">
+      <c r="G31" s="6">
         <v>46197437.789999999</v>
       </c>
-      <c r="F31" s="6">
+      <c r="H31" s="6">
         <v>5632677.2800000003</v>
       </c>
-      <c r="G31" s="7">
+      <c r="I31" s="7">
         <v>51830115.07</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>2024</v>
       </c>
@@ -1362,22 +1553,28 @@
         <v>2091</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" s="6">
+        <v>63780232.719999999</v>
+      </c>
+      <c r="E32" s="6">
+        <v>61454087.810000002</v>
+      </c>
+      <c r="F32" s="6">
         <v>60658393.880000003</v>
       </c>
-      <c r="E32" s="6">
+      <c r="G32" s="6">
         <v>203832.51</v>
       </c>
-      <c r="F32" s="6">
+      <c r="H32" s="6">
         <v>3314473.99</v>
       </c>
-      <c r="G32" s="7">
+      <c r="I32" s="7">
         <v>3518306.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>2024</v>
       </c>
@@ -1385,22 +1582,28 @@
         <v>2101</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6">
+        <v>217344980.62</v>
+      </c>
+      <c r="E33" s="6">
+        <v>207079100.46000001</v>
+      </c>
+      <c r="F33" s="6">
         <v>198091936.58000001</v>
       </c>
-      <c r="E33" s="6">
+      <c r="G33" s="6">
         <v>521685.56</v>
       </c>
-      <c r="F33" s="6">
+      <c r="H33" s="6">
         <v>4299011.63</v>
       </c>
-      <c r="G33" s="7">
+      <c r="I33" s="7">
         <v>4820697.1900000004</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>2024</v>
       </c>
@@ -1408,22 +1611,28 @@
         <v>2121</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6">
+        <v>3010650321.5900002</v>
+      </c>
+      <c r="E34" s="6">
+        <v>2990182081.1199999</v>
+      </c>
+      <c r="F34" s="6">
         <v>2961013745.75</v>
       </c>
-      <c r="E34" s="6">
+      <c r="G34" s="6">
         <v>70175211.909999996</v>
       </c>
-      <c r="F34" s="6">
+      <c r="H34" s="6">
         <v>12134894.130000001</v>
       </c>
-      <c r="G34" s="7">
+      <c r="I34" s="7">
         <v>82310106.040000007</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2024</v>
       </c>
@@ -1431,22 +1640,28 @@
         <v>2151</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="6">
+        <v>88180552.390000001</v>
+      </c>
+      <c r="E35" s="6">
+        <v>80251235.980000004</v>
+      </c>
+      <c r="F35" s="6">
         <v>78333556.760000005</v>
       </c>
-      <c r="E35" s="6">
+      <c r="G35" s="6">
         <v>16912.22</v>
       </c>
-      <c r="F35" s="6">
+      <c r="H35" s="6">
         <v>1852521.82</v>
       </c>
-      <c r="G35" s="7">
+      <c r="I35" s="7">
         <v>1869434.04</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>2024</v>
       </c>
@@ -1454,22 +1669,28 @@
         <v>2161</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D36" s="6">
+        <v>8462182.1600000001</v>
+      </c>
+      <c r="E36" s="6">
+        <v>7716382.4500000002</v>
+      </c>
+      <c r="F36" s="6">
         <v>7622126.71</v>
       </c>
-      <c r="E36" s="6">
+      <c r="G36" s="6">
         <v>256168.61</v>
       </c>
-      <c r="F36" s="6">
+      <c r="H36" s="6">
         <v>287975.89</v>
       </c>
-      <c r="G36" s="7">
+      <c r="I36" s="7">
         <v>544144.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>2024</v>
       </c>
@@ -1477,22 +1698,28 @@
         <v>2171</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D37" s="6">
+        <v>7941833.3700000001</v>
+      </c>
+      <c r="E37" s="6">
+        <v>7516887.29</v>
+      </c>
+      <c r="F37" s="6">
         <v>6813631.04</v>
       </c>
-      <c r="E37" s="6">
+      <c r="G37" s="6">
         <v>55347.98</v>
       </c>
-      <c r="F37" s="6">
+      <c r="H37" s="6">
         <v>249487.78</v>
       </c>
-      <c r="G37" s="7">
+      <c r="I37" s="7">
         <v>304835.76</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>2024</v>
       </c>
@@ -1500,22 +1727,28 @@
         <v>2181</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6">
+        <v>61200638.609999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>58218035.710000001</v>
+      </c>
+      <c r="F38" s="6">
         <v>55031527.640000001</v>
       </c>
-      <c r="E38" s="6">
+      <c r="G38" s="6">
         <v>0</v>
       </c>
-      <c r="F38" s="6">
+      <c r="H38" s="6">
         <v>1781014.41</v>
       </c>
-      <c r="G38" s="7">
+      <c r="I38" s="7">
         <v>1781014.41</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>2024</v>
       </c>
@@ -1523,22 +1756,28 @@
         <v>2201</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="6">
+        <v>32151361.800000001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>29851278.469999999</v>
+      </c>
+      <c r="F39" s="6">
         <v>27723914.949999999</v>
       </c>
-      <c r="E39" s="6">
+      <c r="G39" s="6">
         <v>0.1</v>
       </c>
-      <c r="F39" s="6">
+      <c r="H39" s="6">
         <v>1740955.49</v>
       </c>
-      <c r="G39" s="7">
+      <c r="I39" s="7">
         <v>1740955.59</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>2024</v>
       </c>
@@ -1546,22 +1785,28 @@
         <v>2211</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D40" s="6">
+        <v>18099484.140000001</v>
+      </c>
+      <c r="E40" s="6">
+        <v>16714066.1</v>
+      </c>
+      <c r="F40" s="6">
         <v>15905442.439999999</v>
       </c>
-      <c r="E40" s="6">
+      <c r="G40" s="6">
         <v>333380.82</v>
       </c>
-      <c r="F40" s="6">
+      <c r="H40" s="6">
         <v>636002.17000000004</v>
       </c>
-      <c r="G40" s="7">
+      <c r="I40" s="7">
         <v>969382.99</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>2024</v>
       </c>
@@ -1569,22 +1814,28 @@
         <v>2241</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="6">
+        <v>163783014.55000001</v>
+      </c>
+      <c r="E41" s="6">
+        <v>159345489.81</v>
+      </c>
+      <c r="F41" s="6">
         <v>158705842.44</v>
       </c>
-      <c r="E41" s="6">
+      <c r="G41" s="6">
         <v>28637714.75</v>
       </c>
-      <c r="F41" s="6">
+      <c r="H41" s="6">
         <v>1953947.48</v>
       </c>
-      <c r="G41" s="7">
+      <c r="I41" s="7">
         <v>30591662.23</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>2024</v>
       </c>
@@ -1592,22 +1843,28 @@
         <v>2251</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6">
+        <v>34101030</v>
+      </c>
+      <c r="E42" s="6">
+        <v>32049801.809999999</v>
+      </c>
+      <c r="F42" s="6">
         <v>31364550.07</v>
       </c>
-      <c r="E42" s="6">
+      <c r="G42" s="6">
         <v>99361.65</v>
       </c>
-      <c r="F42" s="6">
+      <c r="H42" s="6">
         <v>974721.99</v>
       </c>
-      <c r="G42" s="7">
+      <c r="I42" s="7">
         <v>1074083.6399999999</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>2024</v>
       </c>
@@ -1615,22 +1872,28 @@
         <v>2261</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
+        <v>617079458.69000006</v>
+      </c>
+      <c r="E43" s="6">
+        <v>457880133.86000001</v>
+      </c>
+      <c r="F43" s="6">
         <v>414275548.19</v>
       </c>
-      <c r="E43" s="6">
+      <c r="G43" s="6">
         <v>915067.75</v>
       </c>
-      <c r="F43" s="6">
+      <c r="H43" s="6">
         <v>52633604.130000003</v>
       </c>
-      <c r="G43" s="7">
+      <c r="I43" s="7">
         <v>53548671.880000003</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2024</v>
       </c>
@@ -1638,22 +1901,28 @@
         <v>2271</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D44" s="6">
+        <v>2332862602.7199998</v>
+      </c>
+      <c r="E44" s="6">
+        <v>2250096399.4099998</v>
+      </c>
+      <c r="F44" s="6">
         <v>2191298111.2800002</v>
       </c>
-      <c r="E44" s="6">
+      <c r="G44" s="6">
         <v>8172915.5300000003</v>
       </c>
-      <c r="F44" s="6">
+      <c r="H44" s="6">
         <v>83039239.159999996</v>
       </c>
-      <c r="G44" s="7">
+      <c r="I44" s="7">
         <v>91212154.689999998</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>2024</v>
       </c>
@@ -1661,22 +1930,28 @@
         <v>2281</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" s="6">
+        <v>6571067.71</v>
+      </c>
+      <c r="E45" s="6">
+        <v>6006116.6900000004</v>
+      </c>
+      <c r="F45" s="6">
         <v>5621531.5899999999</v>
       </c>
-      <c r="E45" s="6">
+      <c r="G45" s="6">
         <v>10063.620000000001</v>
       </c>
-      <c r="F45" s="6">
+      <c r="H45" s="6">
         <v>209239.25</v>
       </c>
-      <c r="G45" s="7">
+      <c r="I45" s="7">
         <v>219302.87</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>2024</v>
       </c>
@@ -1684,22 +1959,28 @@
         <v>2301</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D46" s="6">
+        <v>2166907648.9699998</v>
+      </c>
+      <c r="E46" s="6">
+        <v>1614406418.0699999</v>
+      </c>
+      <c r="F46" s="6">
         <v>1579074300.1199999</v>
       </c>
-      <c r="E46" s="6">
+      <c r="G46" s="6">
         <v>36034587.039999999</v>
       </c>
-      <c r="F46" s="6">
+      <c r="H46" s="6">
         <v>372221350.62</v>
       </c>
-      <c r="G46" s="7">
+      <c r="I46" s="7">
         <v>408255937.66000003</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>2024</v>
       </c>
@@ -1707,22 +1988,28 @@
         <v>2311</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="6">
+        <v>499332522.39999998</v>
+      </c>
+      <c r="E47" s="6">
+        <v>462442399.38</v>
+      </c>
+      <c r="F47" s="6">
         <v>452206130.54000002</v>
       </c>
-      <c r="E47" s="6">
+      <c r="G47" s="6">
         <v>518698.7</v>
       </c>
-      <c r="F47" s="6">
+      <c r="H47" s="6">
         <v>37770634.5</v>
       </c>
-      <c r="G47" s="7">
+      <c r="I47" s="7">
         <v>38289333.200000003</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>2024</v>
       </c>
@@ -1730,22 +2017,28 @@
         <v>2321</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D48" s="6">
+        <v>393216438.36000001</v>
+      </c>
+      <c r="E48" s="6">
+        <v>350212418.49000001</v>
+      </c>
+      <c r="F48" s="6">
         <v>340044994.94999999</v>
       </c>
-      <c r="E48" s="6">
+      <c r="G48" s="6">
         <v>1352290.48</v>
       </c>
-      <c r="F48" s="6">
+      <c r="H48" s="6">
         <v>28148241.670000002</v>
       </c>
-      <c r="G48" s="7">
+      <c r="I48" s="7">
         <v>29500532.149999999</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>2024</v>
       </c>
@@ -1753,22 +2046,28 @@
         <v>2331</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D49" s="6">
+        <v>33811040.590000004</v>
+      </c>
+      <c r="E49" s="6">
+        <v>33218643.649999999</v>
+      </c>
+      <c r="F49" s="6">
         <v>31654005.09</v>
       </c>
-      <c r="E49" s="6">
+      <c r="G49" s="6">
         <v>519444.53</v>
       </c>
-      <c r="F49" s="6">
+      <c r="H49" s="6">
         <v>471410.62</v>
       </c>
-      <c r="G49" s="7">
+      <c r="I49" s="7">
         <v>990855.15</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>2024</v>
       </c>
@@ -1776,22 +2075,28 @@
         <v>2351</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D50" s="6">
+        <v>411019703.14999998</v>
+      </c>
+      <c r="E50" s="6">
+        <v>396207773.82999998</v>
+      </c>
+      <c r="F50" s="6">
         <v>386312319.37</v>
       </c>
-      <c r="E50" s="6">
+      <c r="G50" s="6">
         <v>2944423.8</v>
       </c>
-      <c r="F50" s="6">
+      <c r="H50" s="6">
         <v>10470000.42</v>
       </c>
-      <c r="G50" s="7">
+      <c r="I50" s="7">
         <v>13414424.220000001</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>2024</v>
       </c>
@@ -1799,22 +2104,28 @@
         <v>2371</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D51" s="6">
+        <v>281022284.81</v>
+      </c>
+      <c r="E51" s="6">
+        <v>272651863.27999997</v>
+      </c>
+      <c r="F51" s="6">
         <v>271364090.08999997</v>
       </c>
-      <c r="E51" s="6">
+      <c r="G51" s="6">
         <v>21502.46</v>
       </c>
-      <c r="F51" s="6">
+      <c r="H51" s="6">
         <v>3360355.35</v>
       </c>
-      <c r="G51" s="7">
+      <c r="I51" s="7">
         <v>3381857.81</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>2024</v>
       </c>
@@ -1822,22 +2133,28 @@
         <v>2421</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="6">
+        <v>53824647.210000001</v>
+      </c>
+      <c r="E52" s="6">
+        <v>33871287.270000003</v>
+      </c>
+      <c r="F52" s="6">
         <v>32392034.260000002</v>
       </c>
-      <c r="E52" s="6">
+      <c r="G52" s="6">
         <v>656114.84</v>
       </c>
-      <c r="F52" s="6">
+      <c r="H52" s="6">
         <v>7875523.4800000004</v>
       </c>
-      <c r="G52" s="7">
+      <c r="I52" s="7">
         <v>8531638.3200000003</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2024</v>
       </c>
@@ -1845,22 +2162,28 @@
         <v>2431</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="6">
+        <v>8106389.7300000004</v>
+      </c>
+      <c r="E53" s="6">
+        <v>6808154.4400000004</v>
+      </c>
+      <c r="F53" s="6">
         <v>6635544.6699999999</v>
       </c>
-      <c r="E53" s="6">
+      <c r="G53" s="6">
         <v>0</v>
       </c>
-      <c r="F53" s="6">
+      <c r="H53" s="6">
         <v>554251.69999999995</v>
       </c>
-      <c r="G53" s="7">
+      <c r="I53" s="7">
         <v>554251.69999999995</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>2024</v>
       </c>
@@ -1868,22 +2191,28 @@
         <v>2441</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D54" s="6">
+        <v>18320816.57</v>
+      </c>
+      <c r="E54" s="6">
+        <v>17901288.280000001</v>
+      </c>
+      <c r="F54" s="6">
         <v>17655954.739999998</v>
       </c>
-      <c r="E54" s="6">
+      <c r="G54" s="6">
         <v>151.04</v>
       </c>
-      <c r="F54" s="6">
+      <c r="H54" s="6">
         <v>617418.72</v>
       </c>
-      <c r="G54" s="7">
+      <c r="I54" s="7">
         <v>617569.76</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>2024</v>
       </c>
@@ -1891,361 +2220,451 @@
         <v>2461</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D55" s="6">
+        <v>4028221.25</v>
+      </c>
+      <c r="E55" s="6">
+        <v>3832188.55</v>
+      </c>
+      <c r="F55" s="6">
         <v>3637560.66</v>
       </c>
-      <c r="E55" s="6">
+      <c r="G55" s="6">
         <v>313892.09999999998</v>
       </c>
-      <c r="F55" s="6">
+      <c r="H55" s="6">
         <v>708121.74</v>
       </c>
-      <c r="G55" s="7">
+      <c r="I55" s="7">
         <v>1022013.84</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>2024</v>
       </c>
       <c r="B56" s="4">
+        <v>3041</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="6">
+        <v>399961543.69</v>
+      </c>
+      <c r="E56" s="6">
+        <v>399961543.69</v>
+      </c>
+      <c r="F56" s="6">
+        <v>399961543.69</v>
+      </c>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B57" s="4">
+        <v>3051</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="6">
+        <v>135695037.88</v>
+      </c>
+      <c r="E57" s="6">
+        <v>135695037.88</v>
+      </c>
+      <c r="F57" s="6">
+        <v>135695037.88</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B58" s="4">
         <v>4091</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C58" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>4781856.8899999997</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1781856.89</v>
+      </c>
+      <c r="F58" s="6">
         <v>1780610.81</v>
       </c>
-      <c r="E56" s="6">
+      <c r="G58" s="6">
         <v>1860786.86</v>
       </c>
-      <c r="F56" s="6">
+      <c r="H58" s="6">
         <v>931646.02</v>
       </c>
-      <c r="G56" s="7">
+      <c r="I58" s="7">
         <v>2792432.88</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B57" s="4">
+    <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B59" s="4">
         <v>4101</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C59" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="6">
+        <v>17635213.699999999</v>
+      </c>
+      <c r="E59" s="6">
+        <v>17616149.93</v>
+      </c>
+      <c r="F59" s="6">
         <v>16185012.279999999</v>
       </c>
-      <c r="E57" s="6">
+      <c r="G59" s="6">
         <v>0</v>
       </c>
-      <c r="F57" s="6">
+      <c r="H59" s="6">
         <v>130211.04</v>
       </c>
-      <c r="G57" s="7">
+      <c r="I59" s="7">
         <v>130211.04</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B58" s="4">
+    <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B60" s="4">
         <v>4141</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C60" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="6">
+        <v>32022766.899999999</v>
+      </c>
+      <c r="E60" s="6">
+        <v>22913023.719999999</v>
+      </c>
+      <c r="F60" s="6">
         <v>22137652.859999999</v>
       </c>
-      <c r="E58" s="6">
+      <c r="G60" s="6">
         <v>669506.88</v>
       </c>
-      <c r="F58" s="6">
+      <c r="H60" s="6">
         <v>4513043.66</v>
       </c>
-      <c r="G58" s="7">
+      <c r="I60" s="7">
         <v>5182550.54</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B59" s="4">
+    <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B61" s="4">
         <v>4251</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C61" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="6">
+        <v>191504888.5</v>
+      </c>
+      <c r="E61" s="6">
+        <v>184497317.71000001</v>
+      </c>
+      <c r="F61" s="6">
         <v>182485356.66999999</v>
       </c>
-      <c r="E59" s="6">
+      <c r="G61" s="6">
         <v>811297.6</v>
       </c>
-      <c r="F59" s="6">
+      <c r="H61" s="6">
         <v>3954289.12</v>
       </c>
-      <c r="G59" s="7">
+      <c r="I61" s="7">
         <v>4765586.72</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B60" s="4">
+    <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B62" s="4">
         <v>4291</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C62" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="6">
+        <v>11829504614.639999</v>
+      </c>
+      <c r="E62" s="6">
+        <v>11406407458.040001</v>
+      </c>
+      <c r="F62" s="6">
         <v>11283113714.34</v>
       </c>
-      <c r="E60" s="6">
+      <c r="G62" s="6">
         <v>863891921.10000002</v>
       </c>
-      <c r="F60" s="6">
+      <c r="H62" s="6">
         <v>625577799.00999999</v>
       </c>
-      <c r="G60" s="7">
+      <c r="I62" s="7">
         <v>1489469720.1099999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B61" s="4">
+    <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B63" s="4">
         <v>4331</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="6">
+        <v>1041559.94</v>
+      </c>
+      <c r="E63" s="6">
+        <v>823642.04</v>
+      </c>
+      <c r="F63" s="6">
         <v>813093.72</v>
       </c>
-      <c r="E61" s="6">
+      <c r="G63" s="6">
         <v>0</v>
       </c>
-      <c r="F61" s="6">
+      <c r="H63" s="6">
         <v>0</v>
       </c>
-      <c r="G61" s="7">
+      <c r="I63" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B62" s="4">
+    <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B64" s="4">
         <v>4341</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C64" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="6">
+        <v>4415220.16</v>
+      </c>
+      <c r="E64" s="6">
+        <v>3506542.63</v>
+      </c>
+      <c r="F64" s="6">
         <v>2790383.33</v>
       </c>
-      <c r="E62" s="6">
+      <c r="G64" s="6">
         <v>183731.44</v>
       </c>
-      <c r="F62" s="6">
+      <c r="H64" s="6">
         <v>384241.87</v>
       </c>
-      <c r="G62" s="7">
+      <c r="I64" s="7">
         <v>567973.31000000006</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B63" s="4">
+    <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B65" s="4">
         <v>4381</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C65" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="6">
+        <v>121090271.58</v>
+      </c>
+      <c r="E65" s="6">
+        <v>82874506.280000001</v>
+      </c>
+      <c r="F65" s="6">
         <v>79003714.810000002</v>
       </c>
-      <c r="E63" s="6">
+      <c r="G65" s="6">
         <v>0</v>
       </c>
-      <c r="F63" s="6">
+      <c r="H65" s="6">
         <v>12075855.48</v>
       </c>
-      <c r="G63" s="7">
+      <c r="I65" s="7">
         <v>12075855.48</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B64" s="4">
-        <v>4421</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="6">
-        <v>470000</v>
-      </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="7"/>
-    </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B65" s="4">
+    <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B66" s="4">
         <v>4451</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="C66" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>14312560.43</v>
+      </c>
+      <c r="E66" s="6">
+        <v>8943123.6799999997</v>
+      </c>
+      <c r="F66" s="6">
         <v>8217694.4000000004</v>
       </c>
-      <c r="E65" s="6">
+      <c r="G66" s="6">
         <v>219306.4</v>
       </c>
-      <c r="F65" s="6">
+      <c r="H66" s="6">
         <v>11388620.84</v>
       </c>
-      <c r="G65" s="7">
+      <c r="I66" s="7">
         <v>11607927.24</v>
       </c>
     </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B66" s="4">
+    <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B67" s="4">
         <v>4491</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="6">
+      <c r="C67" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="6">
+        <v>5173333.28</v>
+      </c>
+      <c r="E67" s="6">
+        <v>5153333.28</v>
+      </c>
+      <c r="F67" s="6">
         <v>3822182.56</v>
       </c>
-      <c r="E66" s="6">
+      <c r="G67" s="6">
         <v>50000</v>
       </c>
-      <c r="F66" s="6">
+      <c r="H67" s="6">
         <v>0</v>
       </c>
-      <c r="G66" s="7">
+      <c r="I67" s="7">
         <v>50000</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B67" s="4">
+    <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B68" s="4">
         <v>4541</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="6">
+      <c r="C68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="6">
+        <v>391438.2</v>
+      </c>
+      <c r="E68" s="6">
+        <v>305805.64</v>
+      </c>
+      <c r="F68" s="6">
         <v>288797.78999999998</v>
       </c>
-      <c r="E67" s="6">
+      <c r="G68" s="6">
         <v>0</v>
       </c>
-      <c r="F67" s="6">
+      <c r="H68" s="6">
         <v>26155.45</v>
       </c>
-      <c r="G67" s="7">
+      <c r="I68" s="7">
         <v>26155.45</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B68" s="4">
+    <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B69" s="4">
         <v>4551</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D68" s="6">
+      <c r="C69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="6">
+        <v>239438177.06999999</v>
+      </c>
+      <c r="E69" s="6">
+        <v>238618171.81</v>
+      </c>
+      <c r="F69" s="6">
         <v>238609881.40000001</v>
       </c>
-      <c r="E68" s="6">
+      <c r="G69" s="6">
         <v>9732.9500000000007</v>
       </c>
-      <c r="F68" s="6">
+      <c r="H69" s="6">
         <v>1418075.3</v>
       </c>
-      <c r="G68" s="7">
+      <c r="I69" s="7">
         <v>1427808.25</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B69" s="4">
+    <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B70" s="4">
         <v>4601</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="6">
+      <c r="C70" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="6">
+        <v>5060964</v>
+      </c>
+      <c r="E70" s="6">
+        <v>1670773.97</v>
+      </c>
+      <c r="F70" s="6">
         <v>1595111.21</v>
       </c>
-      <c r="E69" s="6">
+      <c r="G70" s="6">
         <v>0</v>
       </c>
-      <c r="F69" s="6">
+      <c r="H70" s="6">
         <v>0</v>
       </c>
-      <c r="G69" s="7">
+      <c r="I70" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B70" s="4">
-        <v>4631</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="6">
-        <v>356001665.75999999</v>
-      </c>
-      <c r="E70" s="6">
-        <v>6144215.8399999999</v>
-      </c>
-      <c r="F70" s="6">
-        <v>223775960.69999999</v>
-      </c>
-      <c r="G70" s="7">
-        <v>229920176.53999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>2024</v>
       </c>
@@ -2253,22 +2672,28 @@
         <v>4691</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D71" s="6">
+        <v>49389640.210000001</v>
+      </c>
+      <c r="E71" s="6">
+        <v>15901164.57</v>
+      </c>
+      <c r="F71" s="6">
         <v>13533037.66</v>
       </c>
-      <c r="E71" s="6">
+      <c r="G71" s="6">
         <v>1152378.0900000001</v>
       </c>
-      <c r="F71" s="6">
+      <c r="H71" s="6">
         <v>44348538.920000002</v>
       </c>
-      <c r="G71" s="7">
+      <c r="I71" s="7">
         <v>45500917.009999998</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>2024</v>
       </c>
@@ -2276,22 +2701,28 @@
         <v>4701</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D72" s="6">
+        <v>1242375.3</v>
+      </c>
+      <c r="E72" s="6">
+        <v>921616.21</v>
+      </c>
+      <c r="F72" s="6">
         <v>921884.45</v>
       </c>
-      <c r="E72" s="6">
+      <c r="G72" s="6">
         <v>4275.66</v>
       </c>
-      <c r="F72" s="6">
+      <c r="H72" s="6">
         <v>446306.33</v>
       </c>
-      <c r="G72" s="7">
+      <c r="I72" s="7">
         <v>450581.99</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>2024</v>
       </c>
@@ -2299,22 +2730,28 @@
         <v>4711</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D73" s="6">
+        <v>17508957839.759998</v>
+      </c>
+      <c r="E73" s="6">
+        <v>17468843822.73</v>
+      </c>
+      <c r="F73" s="6">
         <v>17473304282.389999</v>
       </c>
-      <c r="E73" s="6">
+      <c r="G73" s="6">
         <v>11281.2</v>
       </c>
-      <c r="F73" s="6">
+      <c r="H73" s="6">
         <v>754605.42</v>
       </c>
-      <c r="G73" s="7">
+      <c r="I73" s="7">
         <v>765886.62</v>
       </c>
     </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\OneDrive\Documents\html\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A1B7763-6DF0-4D90-96F7-09DEAC167AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
+    <t>Unidade Orçamentária - Código/Nome</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Sigla</t>
   </si>
   <si>
     <t>Valor Despesa Empenhada</t>
@@ -48,226 +49,442 @@
     <t>Valor Pago RP</t>
   </si>
   <si>
-    <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>ADVOCACIA GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
-  </si>
-  <si>
-    <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
-  </si>
-  <si>
-    <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE GOVERNO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>CONTROLADORIA-GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA-GERAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
-  </si>
-  <si>
-    <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
-  </si>
-  <si>
-    <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-  </si>
-  <si>
-    <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
-  </si>
-  <si>
-    <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO JOAO PINHEIRO</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HELENA ANTIPOFF</t>
-  </si>
-  <si>
-    <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE ARTE DE OURO PRETO</t>
-  </si>
-  <si>
-    <t>FUNDACAO CLOVIS SALGADO</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
-  </si>
-  <si>
-    <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO EZEQUIEL DIAS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE HABITACAO</t>
-  </si>
-  <si>
-    <t>FUNDO PENITENCIARIO ESTADUAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SAUDE</t>
-  </si>
-  <si>
-    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
-  </si>
-  <si>
-    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE CULTURA</t>
-  </si>
-  <si>
-    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+    <t>1071 - GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>GABINETE MILITAR</t>
+  </si>
+  <si>
+    <t>1081 - ADVOCACIA GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>1101 - OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>OGE</t>
+  </si>
+  <si>
+    <t>1191 - SECRETARIA DE ESTADO DE FAZENDA</t>
+  </si>
+  <si>
+    <t>SEF</t>
+  </si>
+  <si>
+    <t>1221 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>1231 - SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+  </si>
+  <si>
+    <t>SEAPA</t>
+  </si>
+  <si>
+    <t>1251 - POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PMMG</t>
+  </si>
+  <si>
+    <t>1261 - SECRETARIA DE ESTADO DE EDUCACAO</t>
+  </si>
+  <si>
+    <t>SEE</t>
+  </si>
+  <si>
+    <t>1271 - SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+  </si>
+  <si>
+    <t>SECULT</t>
+  </si>
+  <si>
+    <t>1301 - SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+  </si>
+  <si>
+    <t>SEINFRA</t>
+  </si>
+  <si>
+    <t>1371 - SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+  </si>
+  <si>
+    <t>SEMAD</t>
+  </si>
+  <si>
+    <t>1401 - CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>CBMMG</t>
+  </si>
+  <si>
+    <t>1451 - SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+  </si>
+  <si>
+    <t>SEJUSP</t>
+  </si>
+  <si>
+    <t>1481 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+  </si>
+  <si>
+    <t>SEDESE</t>
+  </si>
+  <si>
+    <t>1491 - SECRETARIA DE ESTADO DE GOVERNO</t>
+  </si>
+  <si>
+    <t>SEGOV</t>
+  </si>
+  <si>
+    <t>1501 - SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>SEPLAG</t>
+  </si>
+  <si>
+    <t>1511 - POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PCMG</t>
+  </si>
+  <si>
+    <t>1521 - CONTROLADORIA-GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>CGE</t>
+  </si>
+  <si>
+    <t>1541 - ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ESP MG</t>
+  </si>
+  <si>
+    <t>1631 - SECRETARIA-GERAL</t>
+  </si>
+  <si>
+    <t>SEC. GERAL</t>
+  </si>
+  <si>
+    <t>1711 - SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+  </si>
+  <si>
+    <t>SECOM</t>
+  </si>
+  <si>
+    <t>1721 - SECRETARIA DE ESTADO DA CASA CIVIL</t>
+  </si>
+  <si>
+    <t>SCC</t>
+  </si>
+  <si>
+    <t>1911 - EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+  </si>
+  <si>
+    <t>EGE - SEF</t>
+  </si>
+  <si>
+    <t>1915 - PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+  </si>
+  <si>
+    <t>PARTICIPAÇÃO EMPRESAS</t>
+  </si>
+  <si>
+    <t>1916 - GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+  </si>
+  <si>
+    <t>GDPE - SEF</t>
+  </si>
+  <si>
+    <t>1941 - EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>EGE-SEPLAG</t>
+  </si>
+  <si>
+    <t>2011 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSEMG</t>
+  </si>
+  <si>
+    <t>2041 - LOTERIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>LEMG</t>
+  </si>
+  <si>
+    <t>2061 - FUNDACAO JOAO PINHEIRO</t>
+  </si>
+  <si>
+    <t>FJP</t>
+  </si>
+  <si>
+    <t>2071 - FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAPEMIG</t>
+  </si>
+  <si>
+    <t>2091 - FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>FEAM</t>
+  </si>
+  <si>
+    <t>2101 - INSTITUTO ESTADUAL DE FLORESTAS</t>
+  </si>
+  <si>
+    <t>IEF</t>
+  </si>
+  <si>
+    <t>2121 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSM</t>
+  </si>
+  <si>
+    <t>2151 - FUNDACAO HELENA ANTIPOFF</t>
+  </si>
+  <si>
+    <t>FHA</t>
+  </si>
+  <si>
+    <t>2161 - FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+  </si>
+  <si>
+    <t>FUCAM</t>
+  </si>
+  <si>
+    <t>2171 - FUNDACAO DE ARTE DE OURO PRETO</t>
+  </si>
+  <si>
+    <t>FAOP</t>
+  </si>
+  <si>
+    <t>2181 - FUNDACAO CLOVIS SALGADO</t>
+  </si>
+  <si>
+    <t>FCS</t>
+  </si>
+  <si>
+    <t>2201 - INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IEPHA</t>
+  </si>
+  <si>
+    <t>2211 - FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+  </si>
+  <si>
+    <t>TV MINAS</t>
+  </si>
+  <si>
+    <t>2241 - INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+  </si>
+  <si>
+    <t>IGAM</t>
+  </si>
+  <si>
+    <t>2251 - JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>JUCEMG</t>
+  </si>
+  <si>
+    <t>2261 - FUNDACAO EZEQUIEL DIAS</t>
+  </si>
+  <si>
+    <t>FUNED</t>
+  </si>
+  <si>
+    <t>2271 - FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FHEMIG</t>
+  </si>
+  <si>
+    <t>2281 - FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UTRAMIG</t>
+  </si>
+  <si>
+    <t>2301 - DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>DER-MG</t>
+  </si>
+  <si>
+    <t>2311 - UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>UNIMONTES</t>
+  </si>
+  <si>
+    <t>2321 - FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>HEMOMINAS</t>
+  </si>
+  <si>
+    <t>2331 - INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPEMMG</t>
+  </si>
+  <si>
+    <t>2351 - UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UEMG</t>
+  </si>
+  <si>
+    <t>2371 - INSTITUTO MINEIRO DE AGROPECUARIA</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>2421 - INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IDENE</t>
+  </si>
+  <si>
+    <t>2431 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>AGÊNCIA RMBH</t>
+  </si>
+  <si>
+    <t>2441 - AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+  </si>
+  <si>
+    <t>ARSAE -MG</t>
+  </si>
+  <si>
+    <t>2461 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+  </si>
+  <si>
+    <t>ARMVA</t>
+  </si>
+  <si>
+    <t>3041 - EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMATER</t>
+  </si>
+  <si>
+    <t>3051 - EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EPAMIG</t>
+  </si>
+  <si>
+    <t>4091 - FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+  </si>
+  <si>
+    <t>FIA</t>
+  </si>
+  <si>
+    <t>4101 - FUNDO ESTADUAL DE HABITACAO</t>
+  </si>
+  <si>
+    <t>FEH</t>
+  </si>
+  <si>
+    <t>4141 - FUNDO PENITENCIARIO ESTADUAL</t>
+  </si>
+  <si>
+    <t>FPE</t>
+  </si>
+  <si>
+    <t>4251 - FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>FEAS</t>
+  </si>
+  <si>
+    <t>4291 - FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FES</t>
+  </si>
+  <si>
+    <t>4331 - FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>FDM</t>
+  </si>
+  <si>
+    <t>4341 - FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+  </si>
+  <si>
+    <t>FHIDRO</t>
+  </si>
+  <si>
+    <t>4381 - FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FUNTRANS</t>
+  </si>
+  <si>
+    <t>4451 - FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+  </si>
+  <si>
+    <t>FEPDC</t>
+  </si>
+  <si>
+    <t>4491 - FUNDO ESTADUAL DE CULTURA</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t>4541 - FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAHMEMG</t>
+  </si>
+  <si>
+    <t>4551 - FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNAPEC</t>
+  </si>
+  <si>
+    <t>4601 - FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+  </si>
+  <si>
+    <t>FEI</t>
+  </si>
+  <si>
+    <t>4691 - FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FESP-MG</t>
+  </si>
+  <si>
+    <t>4701 - FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FET-MG</t>
+  </si>
+  <si>
+    <t>4711 - FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FFP - MG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
@@ -381,39 +598,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -446,9 +663,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -481,6 +715,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -542,13 +793,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -557,6 +801,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -621,24 +872,44 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="119.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
     <col min="4" max="6" width="17.28515625" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="25.140625" customWidth="1"/>
@@ -646,14 +917,14 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -679,11 +950,11 @@
       <c r="A2" s="4">
         <v>2024</v>
       </c>
-      <c r="B2" s="4">
-        <v>1071</v>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="6">
         <v>39892772.32</v>
@@ -708,11 +979,11 @@
       <c r="A3" s="4">
         <v>2024</v>
       </c>
-      <c r="B3" s="4">
-        <v>1081</v>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6">
         <v>1176383140.29</v>
@@ -737,11 +1008,11 @@
       <c r="A4" s="4">
         <v>2024</v>
       </c>
-      <c r="B4" s="4">
-        <v>1101</v>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6">
         <v>16775084.75</v>
@@ -766,11 +1037,11 @@
       <c r="A5" s="4">
         <v>2024</v>
       </c>
-      <c r="B5" s="4">
-        <v>1191</v>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6">
         <v>1774005537.77</v>
@@ -795,11 +1066,11 @@
       <c r="A6" s="4">
         <v>2024</v>
       </c>
-      <c r="B6" s="4">
-        <v>1221</v>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6">
         <v>73450042.359999999</v>
@@ -824,11 +1095,11 @@
       <c r="A7" s="4">
         <v>2024</v>
       </c>
-      <c r="B7" s="4">
-        <v>1231</v>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6">
         <v>144310208.36000001</v>
@@ -853,11 +1124,11 @@
       <c r="A8" s="4">
         <v>2024</v>
       </c>
-      <c r="B8" s="4">
-        <v>1251</v>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6">
         <v>14358949915.030001</v>
@@ -882,11 +1153,11 @@
       <c r="A9" s="4">
         <v>2024</v>
       </c>
-      <c r="B9" s="4">
-        <v>1261</v>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6">
         <v>19265871510.98</v>
@@ -911,11 +1182,11 @@
       <c r="A10" s="4">
         <v>2024</v>
       </c>
-      <c r="B10" s="4">
-        <v>1271</v>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>278574229.64999998</v>
@@ -940,11 +1211,11 @@
       <c r="A11" s="4">
         <v>2024</v>
       </c>
-      <c r="B11" s="4">
-        <v>1301</v>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
         <v>739415330.30999994</v>
@@ -969,11 +1240,11 @@
       <c r="A12" s="4">
         <v>2024</v>
       </c>
-      <c r="B12" s="4">
-        <v>1371</v>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D12" s="6">
         <v>184730264.22999999</v>
@@ -998,11 +1269,11 @@
       <c r="A13" s="4">
         <v>2024</v>
       </c>
-      <c r="B13" s="4">
-        <v>1401</v>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>1689247203.3900001</v>
@@ -1027,11 +1298,11 @@
       <c r="A14" s="4">
         <v>2024</v>
       </c>
-      <c r="B14" s="4">
-        <v>1451</v>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
         <v>4151305223.1199999</v>
@@ -1056,11 +1327,11 @@
       <c r="A15" s="4">
         <v>2024</v>
       </c>
-      <c r="B15" s="4">
-        <v>1481</v>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
         <v>192351891.56999999</v>
@@ -1085,11 +1356,11 @@
       <c r="A16" s="4">
         <v>2024</v>
       </c>
-      <c r="B16" s="4">
-        <v>1491</v>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6">
         <v>936918721.66999996</v>
@@ -1114,11 +1385,11 @@
       <c r="A17" s="4">
         <v>2024</v>
       </c>
-      <c r="B17" s="4">
-        <v>1501</v>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6">
         <v>855546794.05999994</v>
@@ -1143,11 +1414,11 @@
       <c r="A18" s="4">
         <v>2024</v>
       </c>
-      <c r="B18" s="4">
-        <v>1511</v>
+      <c r="B18" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6">
         <v>2971107807.8499999</v>
@@ -1172,11 +1443,11 @@
       <c r="A19" s="4">
         <v>2024</v>
       </c>
-      <c r="B19" s="4">
-        <v>1521</v>
+      <c r="B19" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D19" s="6">
         <v>67525357.700000003</v>
@@ -1201,11 +1472,11 @@
       <c r="A20" s="4">
         <v>2024</v>
       </c>
-      <c r="B20" s="4">
-        <v>1541</v>
+      <c r="B20" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D20" s="6">
         <v>21259443.359999999</v>
@@ -1230,11 +1501,11 @@
       <c r="A21" s="4">
         <v>2024</v>
       </c>
-      <c r="B21" s="4">
-        <v>1631</v>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D21" s="6">
         <v>9422516.7100000009</v>
@@ -1259,11 +1530,11 @@
       <c r="A22" s="4">
         <v>2024</v>
       </c>
-      <c r="B22" s="4">
-        <v>1711</v>
+      <c r="B22" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6">
         <v>145415971.84</v>
@@ -1288,11 +1559,11 @@
       <c r="A23" s="4">
         <v>2024</v>
       </c>
-      <c r="B23" s="4">
-        <v>1721</v>
+      <c r="B23" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D23" s="6">
         <v>11376822.58</v>
@@ -1317,11 +1588,11 @@
       <c r="A24" s="4">
         <v>2024</v>
       </c>
-      <c r="B24" s="4">
-        <v>1911</v>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D24" s="6">
         <v>1542024334.1800001</v>
@@ -1346,11 +1617,11 @@
       <c r="A25" s="4">
         <v>2024</v>
       </c>
-      <c r="B25" s="4">
-        <v>1915</v>
+      <c r="B25" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D25" s="6">
         <v>77370454.079999998</v>
@@ -1375,11 +1646,11 @@
       <c r="A26" s="4">
         <v>2024</v>
       </c>
-      <c r="B26" s="4">
-        <v>1916</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D26" s="6">
         <v>3797673691.6900001</v>
@@ -1404,11 +1675,11 @@
       <c r="A27" s="4">
         <v>2024</v>
       </c>
-      <c r="B27" s="4">
-        <v>1941</v>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D27" s="6">
         <v>198068287.50999999</v>
@@ -1433,11 +1704,11 @@
       <c r="A28" s="4">
         <v>2024</v>
       </c>
-      <c r="B28" s="4">
-        <v>2011</v>
+      <c r="B28" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D28" s="6">
         <v>1725474955.8</v>
@@ -1462,11 +1733,11 @@
       <c r="A29" s="4">
         <v>2024</v>
       </c>
-      <c r="B29" s="4">
-        <v>2041</v>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D29" s="6">
         <v>2753285.11</v>
@@ -1491,11 +1762,11 @@
       <c r="A30" s="4">
         <v>2024</v>
       </c>
-      <c r="B30" s="4">
-        <v>2061</v>
+      <c r="B30" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D30" s="6">
         <v>69147295.900000006</v>
@@ -1520,11 +1791,11 @@
       <c r="A31" s="4">
         <v>2024</v>
       </c>
-      <c r="B31" s="4">
-        <v>2071</v>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D31" s="6">
         <v>533594583.23000002</v>
@@ -1549,11 +1820,11 @@
       <c r="A32" s="4">
         <v>2024</v>
       </c>
-      <c r="B32" s="4">
-        <v>2091</v>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6">
         <v>63780232.719999999</v>
@@ -1578,11 +1849,11 @@
       <c r="A33" s="4">
         <v>2024</v>
       </c>
-      <c r="B33" s="4">
-        <v>2101</v>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6">
         <v>217344980.62</v>
@@ -1607,11 +1878,11 @@
       <c r="A34" s="4">
         <v>2024</v>
       </c>
-      <c r="B34" s="4">
-        <v>2121</v>
+      <c r="B34" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D34" s="6">
         <v>3010650321.5900002</v>
@@ -1636,11 +1907,11 @@
       <c r="A35" s="4">
         <v>2024</v>
       </c>
-      <c r="B35" s="4">
-        <v>2151</v>
+      <c r="B35" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D35" s="6">
         <v>88180552.390000001</v>
@@ -1665,11 +1936,11 @@
       <c r="A36" s="4">
         <v>2024</v>
       </c>
-      <c r="B36" s="4">
-        <v>2161</v>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D36" s="6">
         <v>8462182.1600000001</v>
@@ -1694,11 +1965,11 @@
       <c r="A37" s="4">
         <v>2024</v>
       </c>
-      <c r="B37" s="4">
-        <v>2171</v>
+      <c r="B37" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D37" s="6">
         <v>7941833.3700000001</v>
@@ -1723,11 +1994,11 @@
       <c r="A38" s="4">
         <v>2024</v>
       </c>
-      <c r="B38" s="4">
-        <v>2181</v>
+      <c r="B38" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D38" s="6">
         <v>61200638.609999999</v>
@@ -1752,11 +2023,11 @@
       <c r="A39" s="4">
         <v>2024</v>
       </c>
-      <c r="B39" s="4">
-        <v>2201</v>
+      <c r="B39" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6">
         <v>32151361.800000001</v>
@@ -1781,11 +2052,11 @@
       <c r="A40" s="4">
         <v>2024</v>
       </c>
-      <c r="B40" s="4">
-        <v>2211</v>
+      <c r="B40" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="D40" s="6">
         <v>18099484.140000001</v>
@@ -1810,11 +2081,11 @@
       <c r="A41" s="4">
         <v>2024</v>
       </c>
-      <c r="B41" s="4">
-        <v>2241</v>
+      <c r="B41" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D41" s="6">
         <v>163783014.55000001</v>
@@ -1839,11 +2110,11 @@
       <c r="A42" s="4">
         <v>2024</v>
       </c>
-      <c r="B42" s="4">
-        <v>2251</v>
+      <c r="B42" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6">
         <v>34101030</v>
@@ -1868,11 +2139,11 @@
       <c r="A43" s="4">
         <v>2024</v>
       </c>
-      <c r="B43" s="4">
-        <v>2261</v>
+      <c r="B43" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6">
         <v>617079458.69000006</v>
@@ -1897,11 +2168,11 @@
       <c r="A44" s="4">
         <v>2024</v>
       </c>
-      <c r="B44" s="4">
-        <v>2271</v>
+      <c r="B44" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D44" s="6">
         <v>2332862602.7199998</v>
@@ -1926,11 +2197,11 @@
       <c r="A45" s="4">
         <v>2024</v>
       </c>
-      <c r="B45" s="4">
-        <v>2281</v>
+      <c r="B45" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D45" s="6">
         <v>6571067.71</v>
@@ -1955,11 +2226,11 @@
       <c r="A46" s="4">
         <v>2024</v>
       </c>
-      <c r="B46" s="4">
-        <v>2301</v>
+      <c r="B46" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D46" s="6">
         <v>2166907648.9699998</v>
@@ -1984,11 +2255,11 @@
       <c r="A47" s="4">
         <v>2024</v>
       </c>
-      <c r="B47" s="4">
-        <v>2311</v>
+      <c r="B47" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="D47" s="6">
         <v>499332522.39999998</v>
@@ -2013,11 +2284,11 @@
       <c r="A48" s="4">
         <v>2024</v>
       </c>
-      <c r="B48" s="4">
-        <v>2321</v>
+      <c r="B48" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D48" s="6">
         <v>393216438.36000001</v>
@@ -2042,11 +2313,11 @@
       <c r="A49" s="4">
         <v>2024</v>
       </c>
-      <c r="B49" s="4">
-        <v>2331</v>
+      <c r="B49" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D49" s="6">
         <v>33811040.590000004</v>
@@ -2071,11 +2342,11 @@
       <c r="A50" s="4">
         <v>2024</v>
       </c>
-      <c r="B50" s="4">
-        <v>2351</v>
+      <c r="B50" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D50" s="6">
         <v>411019703.14999998</v>
@@ -2100,11 +2371,11 @@
       <c r="A51" s="4">
         <v>2024</v>
       </c>
-      <c r="B51" s="4">
-        <v>2371</v>
+      <c r="B51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D51" s="6">
         <v>281022284.81</v>
@@ -2129,11 +2400,11 @@
       <c r="A52" s="4">
         <v>2024</v>
       </c>
-      <c r="B52" s="4">
-        <v>2421</v>
+      <c r="B52" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D52" s="6">
         <v>53824647.210000001</v>
@@ -2158,11 +2429,11 @@
       <c r="A53" s="4">
         <v>2024</v>
       </c>
-      <c r="B53" s="4">
-        <v>2431</v>
+      <c r="B53" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D53" s="6">
         <v>8106389.7300000004</v>
@@ -2187,11 +2458,11 @@
       <c r="A54" s="4">
         <v>2024</v>
       </c>
-      <c r="B54" s="4">
-        <v>2441</v>
+      <c r="B54" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D54" s="6">
         <v>18320816.57</v>
@@ -2216,11 +2487,11 @@
       <c r="A55" s="4">
         <v>2024</v>
       </c>
-      <c r="B55" s="4">
-        <v>2461</v>
+      <c r="B55" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D55" s="6">
         <v>4028221.25</v>
@@ -2245,11 +2516,11 @@
       <c r="A56" s="4">
         <v>2024</v>
       </c>
-      <c r="B56" s="4">
-        <v>3041</v>
+      <c r="B56" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="D56" s="6">
         <v>399961543.69</v>
@@ -2268,11 +2539,11 @@
       <c r="A57" s="4">
         <v>2024</v>
       </c>
-      <c r="B57" s="4">
-        <v>3051</v>
+      <c r="B57" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6">
         <v>135695037.88</v>
@@ -2291,11 +2562,11 @@
       <c r="A58" s="4">
         <v>2024</v>
       </c>
-      <c r="B58" s="4">
-        <v>4091</v>
+      <c r="B58" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="D58" s="6">
         <v>4781856.8899999997</v>
@@ -2320,11 +2591,11 @@
       <c r="A59" s="4">
         <v>2024</v>
       </c>
-      <c r="B59" s="4">
-        <v>4101</v>
+      <c r="B59" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D59" s="6">
         <v>17635213.699999999</v>
@@ -2349,11 +2620,11 @@
       <c r="A60" s="4">
         <v>2024</v>
       </c>
-      <c r="B60" s="4">
-        <v>4141</v>
+      <c r="B60" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D60" s="6">
         <v>32022766.899999999</v>
@@ -2378,11 +2649,11 @@
       <c r="A61" s="4">
         <v>2024</v>
       </c>
-      <c r="B61" s="4">
-        <v>4251</v>
+      <c r="B61" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D61" s="6">
         <v>191504888.5</v>
@@ -2407,11 +2678,11 @@
       <c r="A62" s="4">
         <v>2024</v>
       </c>
-      <c r="B62" s="4">
-        <v>4291</v>
+      <c r="B62" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D62" s="6">
         <v>11829504614.639999</v>
@@ -2436,11 +2707,11 @@
       <c r="A63" s="4">
         <v>2024</v>
       </c>
-      <c r="B63" s="4">
-        <v>4331</v>
+      <c r="B63" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D63" s="6">
         <v>1041559.94</v>
@@ -2465,11 +2736,11 @@
       <c r="A64" s="4">
         <v>2024</v>
       </c>
-      <c r="B64" s="4">
-        <v>4341</v>
+      <c r="B64" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D64" s="6">
         <v>4415220.16</v>
@@ -2494,11 +2765,11 @@
       <c r="A65" s="4">
         <v>2024</v>
       </c>
-      <c r="B65" s="4">
-        <v>4381</v>
+      <c r="B65" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D65" s="6">
         <v>121090271.58</v>
@@ -2523,11 +2794,11 @@
       <c r="A66" s="4">
         <v>2024</v>
       </c>
-      <c r="B66" s="4">
-        <v>4451</v>
+      <c r="B66" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="D66" s="6">
         <v>14312560.43</v>
@@ -2552,11 +2823,11 @@
       <c r="A67" s="4">
         <v>2024</v>
       </c>
-      <c r="B67" s="4">
-        <v>4491</v>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="D67" s="6">
         <v>5173333.28</v>
@@ -2581,11 +2852,11 @@
       <c r="A68" s="4">
         <v>2024</v>
       </c>
-      <c r="B68" s="4">
-        <v>4541</v>
+      <c r="B68" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D68" s="6">
         <v>391438.2</v>
@@ -2610,11 +2881,11 @@
       <c r="A69" s="4">
         <v>2024</v>
       </c>
-      <c r="B69" s="4">
-        <v>4551</v>
+      <c r="B69" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="D69" s="6">
         <v>239438177.06999999</v>
@@ -2639,11 +2910,11 @@
       <c r="A70" s="4">
         <v>2024</v>
       </c>
-      <c r="B70" s="4">
-        <v>4601</v>
+      <c r="B70" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D70" s="6">
         <v>5060964</v>
@@ -2668,11 +2939,11 @@
       <c r="A71" s="4">
         <v>2024</v>
       </c>
-      <c r="B71" s="4">
-        <v>4691</v>
+      <c r="B71" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D71" s="6">
         <v>49389640.210000001</v>
@@ -2697,11 +2968,11 @@
       <c r="A72" s="4">
         <v>2024</v>
       </c>
-      <c r="B72" s="4">
-        <v>4701</v>
+      <c r="B72" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="D72" s="6">
         <v>1242375.3</v>
@@ -2726,11 +2997,11 @@
       <c r="A73" s="4">
         <v>2024</v>
       </c>
-      <c r="B73" s="4">
-        <v>4711</v>
+      <c r="B73" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="D73" s="6">
         <v>17508957839.759998</v>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,25 +840,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3051</v>
+        <v>3151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135695037.88</v>
+        <v>29599261.39</v>
       </c>
       <c r="F12" t="n">
-        <v>135695037.88</v>
+        <v>29599261.39</v>
       </c>
       <c r="G12" t="n">
-        <v>135695037.88</v>
+        <v>29599261.39</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -870,35 +870,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21259443.36</v>
+        <v>135695037.88</v>
       </c>
       <c r="F13" t="n">
-        <v>20594781.94</v>
+        <v>135695037.88</v>
       </c>
       <c r="G13" t="n">
-        <v>20198969.09</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11884.85</v>
-      </c>
-      <c r="I13" t="n">
-        <v>215304.71</v>
-      </c>
-      <c r="J13" t="n">
-        <v>227189.56</v>
-      </c>
+        <v>135695037.88</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -906,34 +900,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>391438.2</v>
+        <v>21259443.36</v>
       </c>
       <c r="F14" t="n">
-        <v>305805.64</v>
+        <v>20594781.94</v>
       </c>
       <c r="G14" t="n">
-        <v>288797.79</v>
+        <v>20198969.09</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>11884.85</v>
       </c>
       <c r="I14" t="n">
-        <v>26155.45</v>
+        <v>215304.71</v>
       </c>
       <c r="J14" t="n">
-        <v>26155.45</v>
+        <v>227189.56</v>
       </c>
     </row>
     <row r="15">
@@ -942,34 +936,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7941833.37</v>
+        <v>391438.2</v>
       </c>
       <c r="F15" t="n">
-        <v>7516887.29</v>
+        <v>305805.64</v>
       </c>
       <c r="G15" t="n">
-        <v>6813631.04</v>
+        <v>288797.79</v>
       </c>
       <c r="H15" t="n">
-        <v>55347.98</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>249487.78</v>
+        <v>26155.45</v>
       </c>
       <c r="J15" t="n">
-        <v>304835.76</v>
+        <v>26155.45</v>
       </c>
     </row>
     <row r="16">
@@ -978,34 +972,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>533594583.23</v>
+        <v>7941833.37</v>
       </c>
       <c r="F16" t="n">
-        <v>523602791.54</v>
+        <v>7516887.29</v>
       </c>
       <c r="G16" t="n">
-        <v>524266165.17</v>
+        <v>6813631.04</v>
       </c>
       <c r="H16" t="n">
-        <v>46197437.79</v>
+        <v>55347.98</v>
       </c>
       <c r="I16" t="n">
-        <v>5632677.28</v>
+        <v>249487.78</v>
       </c>
       <c r="J16" t="n">
-        <v>51830115.07</v>
+        <v>304835.76</v>
       </c>
     </row>
     <row r="17">
@@ -1014,34 +1008,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>61200638.61</v>
+        <v>533594583.23</v>
       </c>
       <c r="F17" t="n">
-        <v>58218035.71</v>
+        <v>523602791.54</v>
       </c>
       <c r="G17" t="n">
-        <v>55031527.64</v>
+        <v>524266165.17</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>46197437.79</v>
       </c>
       <c r="I17" t="n">
-        <v>1781014.41</v>
+        <v>5632677.28</v>
       </c>
       <c r="J17" t="n">
-        <v>1781014.41</v>
+        <v>51830115.07</v>
       </c>
     </row>
     <row r="18">
@@ -1050,34 +1044,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1041559.94</v>
+        <v>61200638.61</v>
       </c>
       <c r="F18" t="n">
-        <v>823642.04</v>
+        <v>58218035.71</v>
       </c>
       <c r="G18" t="n">
-        <v>813093.72</v>
+        <v>55031527.64</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1781014.41</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1781014.41</v>
       </c>
     </row>
     <row r="19">
@@ -1086,34 +1080,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63780232.72</v>
+        <v>1041559.94</v>
       </c>
       <c r="F19" t="n">
-        <v>61454087.81</v>
+        <v>823642.04</v>
       </c>
       <c r="G19" t="n">
-        <v>60658393.88</v>
+        <v>813093.72</v>
       </c>
       <c r="H19" t="n">
-        <v>203832.51</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3314473.99</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3518306.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1122,34 +1116,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>191504888.5</v>
+        <v>63780232.72</v>
       </c>
       <c r="F20" t="n">
-        <v>184497317.71</v>
+        <v>61454087.81</v>
       </c>
       <c r="G20" t="n">
-        <v>182485356.67</v>
+        <v>60658393.88</v>
       </c>
       <c r="H20" t="n">
-        <v>811297.6</v>
+        <v>203832.51</v>
       </c>
       <c r="I20" t="n">
-        <v>3954289.12</v>
+        <v>3314473.99</v>
       </c>
       <c r="J20" t="n">
-        <v>4765586.72</v>
+        <v>3518306.5</v>
       </c>
     </row>
     <row r="21">
@@ -1158,34 +1152,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5173333.28</v>
+        <v>191504888.5</v>
       </c>
       <c r="F21" t="n">
-        <v>5153333.28</v>
+        <v>184497317.71</v>
       </c>
       <c r="G21" t="n">
-        <v>3822182.56</v>
+        <v>182485356.67</v>
       </c>
       <c r="H21" t="n">
-        <v>50000</v>
+        <v>811297.6</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>3954289.12</v>
       </c>
       <c r="J21" t="n">
-        <v>50000</v>
+        <v>4765586.72</v>
       </c>
     </row>
     <row r="22">
@@ -1194,34 +1188,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17635213.7</v>
+        <v>5173333.28</v>
       </c>
       <c r="F22" t="n">
-        <v>17616149.93</v>
+        <v>5153333.28</v>
       </c>
       <c r="G22" t="n">
-        <v>16185012.28</v>
+        <v>3822182.56</v>
       </c>
       <c r="H22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
-        <v>130211.04</v>
-      </c>
       <c r="J22" t="n">
-        <v>130211.04</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="23">
@@ -1230,34 +1224,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5060964</v>
+        <v>17635213.7</v>
       </c>
       <c r="F23" t="n">
-        <v>1670773.97</v>
+        <v>17616149.93</v>
       </c>
       <c r="G23" t="n">
-        <v>1595111.21</v>
+        <v>16185012.28</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>130211.04</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>130211.04</v>
       </c>
     </row>
     <row r="24">
@@ -1266,34 +1260,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>14312560.43</v>
+        <v>5060964</v>
       </c>
       <c r="F24" t="n">
-        <v>8943123.68</v>
+        <v>1670773.97</v>
       </c>
       <c r="G24" t="n">
-        <v>8217694.4</v>
+        <v>1595111.21</v>
       </c>
       <c r="H24" t="n">
-        <v>219306.4</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>11388620.84</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11607927.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1662,34 +1656,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8462182.16</v>
+        <v>497939201.43</v>
       </c>
       <c r="F35" t="n">
-        <v>7716382.45</v>
+        <v>379996046.23</v>
       </c>
       <c r="G35" t="n">
-        <v>7622126.71</v>
+        <v>356001665.76</v>
       </c>
       <c r="H35" t="n">
-        <v>256168.61</v>
+        <v>6144215.84</v>
       </c>
       <c r="I35" t="n">
-        <v>287975.89</v>
+        <v>223775960.7</v>
       </c>
       <c r="J35" t="n">
-        <v>544144.5</v>
+        <v>229920176.54</v>
       </c>
     </row>
     <row r="36">
@@ -1698,34 +1692,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>239438177.07</v>
+        <v>8462182.16</v>
       </c>
       <c r="F36" t="n">
-        <v>238618171.81</v>
+        <v>7716382.45</v>
       </c>
       <c r="G36" t="n">
-        <v>238609881.4</v>
+        <v>7622126.71</v>
       </c>
       <c r="H36" t="n">
-        <v>9732.950000000001</v>
+        <v>256168.61</v>
       </c>
       <c r="I36" t="n">
-        <v>1418075.3</v>
+        <v>287975.89</v>
       </c>
       <c r="J36" t="n">
-        <v>1427808.25</v>
+        <v>544144.5</v>
       </c>
     </row>
     <row r="37">
@@ -1734,34 +1728,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2261</v>
+        <v>4551</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>617079458.6900001</v>
+        <v>239438177.07</v>
       </c>
       <c r="F37" t="n">
-        <v>457880133.86</v>
+        <v>238618171.81</v>
       </c>
       <c r="G37" t="n">
-        <v>414275548.19</v>
+        <v>238609881.4</v>
       </c>
       <c r="H37" t="n">
-        <v>915067.75</v>
+        <v>9732.950000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>52633604.13</v>
+        <v>1418075.3</v>
       </c>
       <c r="J37" t="n">
-        <v>53548671.88</v>
+        <v>1427808.25</v>
       </c>
     </row>
     <row r="38">
@@ -1770,35 +1764,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4381</v>
+        <v>4421</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>121090271.58</v>
+        <v>490000</v>
       </c>
       <c r="F38" t="n">
-        <v>82874506.28</v>
+        <v>470895.13</v>
       </c>
       <c r="G38" t="n">
-        <v>79003714.81</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>12075855.48</v>
-      </c>
-      <c r="J38" t="n">
-        <v>12075855.48</v>
-      </c>
+        <v>470000</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1806,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1071</v>
+        <v>2261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>39892772.32</v>
+        <v>617079458.6900001</v>
       </c>
       <c r="F39" t="n">
-        <v>35166360.52</v>
+        <v>457880133.86</v>
       </c>
       <c r="G39" t="n">
-        <v>34432753.31</v>
+        <v>414275548.19</v>
       </c>
       <c r="H39" t="n">
-        <v>630087.11</v>
+        <v>915067.75</v>
       </c>
       <c r="I39" t="n">
-        <v>7450507.6</v>
+        <v>52633604.13</v>
       </c>
       <c r="J39" t="n">
-        <v>8080594.71</v>
+        <v>53548671.88</v>
       </c>
     </row>
     <row r="40">
@@ -1842,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1916</v>
+        <v>4381</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3797673691.69</v>
+        <v>121090271.58</v>
       </c>
       <c r="F40" t="n">
-        <v>3797673691.69</v>
+        <v>82874506.28</v>
       </c>
       <c r="G40" t="n">
-        <v>3525271258.01</v>
+        <v>79003714.81</v>
       </c>
       <c r="H40" t="n">
-        <v>158424713.64</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>12075855.48</v>
       </c>
       <c r="J40" t="n">
-        <v>158424713.64</v>
+        <v>12075855.48</v>
       </c>
     </row>
     <row r="41">
@@ -1878,34 +1866,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2321</v>
+        <v>1071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>393216438.36</v>
+        <v>39892772.32</v>
       </c>
       <c r="F41" t="n">
-        <v>350212418.49</v>
+        <v>35166360.52</v>
       </c>
       <c r="G41" t="n">
-        <v>340044994.95</v>
+        <v>34432753.31</v>
       </c>
       <c r="H41" t="n">
-        <v>1352290.48</v>
+        <v>630087.11</v>
       </c>
       <c r="I41" t="n">
-        <v>28148241.67</v>
+        <v>7450507.6</v>
       </c>
       <c r="J41" t="n">
-        <v>29500532.15</v>
+        <v>8080594.71</v>
       </c>
     </row>
     <row r="42">
@@ -1914,34 +1902,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2421</v>
+        <v>1916</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53824647.21</v>
+        <v>3797673691.69</v>
       </c>
       <c r="F42" t="n">
-        <v>33871287.27</v>
+        <v>3797673691.69</v>
       </c>
       <c r="G42" t="n">
-        <v>32392034.26</v>
+        <v>3525271258.01</v>
       </c>
       <c r="H42" t="n">
-        <v>656114.84</v>
+        <v>158424713.64</v>
       </c>
       <c r="I42" t="n">
-        <v>7875523.48</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>8531638.32</v>
+        <v>158424713.64</v>
       </c>
     </row>
     <row r="43">
@@ -1950,34 +1938,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2101</v>
+        <v>2321</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>217344980.62</v>
+        <v>393216438.36</v>
       </c>
       <c r="F43" t="n">
-        <v>207079100.46</v>
+        <v>350212418.49</v>
       </c>
       <c r="G43" t="n">
-        <v>198091936.58</v>
+        <v>340044994.95</v>
       </c>
       <c r="H43" t="n">
-        <v>521685.56</v>
+        <v>1352290.48</v>
       </c>
       <c r="I43" t="n">
-        <v>4299011.63</v>
+        <v>28148241.67</v>
       </c>
       <c r="J43" t="n">
-        <v>4820697.19</v>
+        <v>29500532.15</v>
       </c>
     </row>
     <row r="44">
@@ -1986,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2201</v>
+        <v>2421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>32151361.8</v>
+        <v>53824647.21</v>
       </c>
       <c r="F44" t="n">
-        <v>29851278.47</v>
+        <v>33871287.27</v>
       </c>
       <c r="G44" t="n">
-        <v>27723914.95</v>
+        <v>32392034.26</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1</v>
+        <v>656114.84</v>
       </c>
       <c r="I44" t="n">
-        <v>1740955.49</v>
+        <v>7875523.48</v>
       </c>
       <c r="J44" t="n">
-        <v>1740955.59</v>
+        <v>8531638.32</v>
       </c>
     </row>
     <row r="45">
@@ -2022,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>163783014.55</v>
+        <v>217344980.62</v>
       </c>
       <c r="F45" t="n">
-        <v>159345489.81</v>
+        <v>207079100.46</v>
       </c>
       <c r="G45" t="n">
-        <v>158705842.44</v>
+        <v>198091936.58</v>
       </c>
       <c r="H45" t="n">
-        <v>28637714.75</v>
+        <v>521685.56</v>
       </c>
       <c r="I45" t="n">
-        <v>1953947.48</v>
+        <v>4299011.63</v>
       </c>
       <c r="J45" t="n">
-        <v>30591662.23</v>
+        <v>4820697.19</v>
       </c>
     </row>
     <row r="46">
@@ -2058,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2371</v>
+        <v>2201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>281022284.81</v>
+        <v>32151361.8</v>
       </c>
       <c r="F46" t="n">
-        <v>272651863.28</v>
+        <v>29851278.47</v>
       </c>
       <c r="G46" t="n">
-        <v>271364090.09</v>
+        <v>27723914.95</v>
       </c>
       <c r="H46" t="n">
-        <v>21502.46</v>
+        <v>0.1</v>
       </c>
       <c r="I46" t="n">
-        <v>3360355.35</v>
+        <v>1740955.49</v>
       </c>
       <c r="J46" t="n">
-        <v>3381857.81</v>
+        <v>1740955.59</v>
       </c>
     </row>
     <row r="47">
@@ -2094,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2331</v>
+        <v>2241</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>33811040.59</v>
+        <v>163783014.55</v>
       </c>
       <c r="F47" t="n">
-        <v>33218643.65</v>
+        <v>159345489.81</v>
       </c>
       <c r="G47" t="n">
-        <v>31654005.09</v>
+        <v>158705842.44</v>
       </c>
       <c r="H47" t="n">
-        <v>519444.53</v>
+        <v>28637714.75</v>
       </c>
       <c r="I47" t="n">
-        <v>471410.62</v>
+        <v>1953947.48</v>
       </c>
       <c r="J47" t="n">
-        <v>990855.15</v>
+        <v>30591662.23</v>
       </c>
     </row>
     <row r="48">
@@ -2130,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2011</v>
+        <v>2371</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1725474955.8</v>
+        <v>281022284.81</v>
       </c>
       <c r="F48" t="n">
-        <v>1598962422.88</v>
+        <v>272651863.28</v>
       </c>
       <c r="G48" t="n">
-        <v>1555299505.74</v>
+        <v>271364090.09</v>
       </c>
       <c r="H48" t="n">
-        <v>1217572.7</v>
+        <v>21502.46</v>
       </c>
       <c r="I48" t="n">
-        <v>166587616.35</v>
+        <v>3360355.35</v>
       </c>
       <c r="J48" t="n">
-        <v>167805189.05</v>
+        <v>3381857.81</v>
       </c>
     </row>
     <row r="49">
@@ -2166,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2121</v>
+        <v>2331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3010650321.59</v>
+        <v>33811040.59</v>
       </c>
       <c r="F49" t="n">
-        <v>2990182081.12</v>
+        <v>33218643.65</v>
       </c>
       <c r="G49" t="n">
-        <v>2961013745.75</v>
+        <v>31654005.09</v>
       </c>
       <c r="H49" t="n">
-        <v>70175211.91</v>
+        <v>519444.53</v>
       </c>
       <c r="I49" t="n">
-        <v>12134894.13</v>
+        <v>471410.62</v>
       </c>
       <c r="J49" t="n">
-        <v>82310106.04000001</v>
+        <v>990855.15</v>
       </c>
     </row>
     <row r="50">
@@ -2202,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2251</v>
+        <v>2011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>34101030</v>
+        <v>1725474955.8</v>
       </c>
       <c r="F50" t="n">
-        <v>32049801.81</v>
+        <v>1598962422.88</v>
       </c>
       <c r="G50" t="n">
-        <v>31364550.07</v>
+        <v>1555299505.74</v>
       </c>
       <c r="H50" t="n">
-        <v>99361.64999999999</v>
+        <v>1217572.7</v>
       </c>
       <c r="I50" t="n">
-        <v>974721.99</v>
+        <v>166587616.35</v>
       </c>
       <c r="J50" t="n">
-        <v>1074083.64</v>
+        <v>167805189.05</v>
       </c>
     </row>
     <row r="51">
@@ -2238,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2041</v>
+        <v>2121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2753285.11</v>
+        <v>3010650321.59</v>
       </c>
       <c r="F51" t="n">
-        <v>2718960.43</v>
+        <v>2990182081.12</v>
       </c>
       <c r="G51" t="n">
-        <v>2712294.25</v>
+        <v>2961013745.75</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>70175211.91</v>
       </c>
       <c r="I51" t="n">
-        <v>52615.45</v>
+        <v>12134894.13</v>
       </c>
       <c r="J51" t="n">
-        <v>52615.45</v>
+        <v>82310106.04000001</v>
       </c>
     </row>
     <row r="52">
@@ -2274,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1101</v>
+        <v>2251</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>16775084.75</v>
+        <v>34101030</v>
       </c>
       <c r="F52" t="n">
-        <v>16686029.56</v>
+        <v>32049801.81</v>
       </c>
       <c r="G52" t="n">
-        <v>16501107.08</v>
+        <v>31364550.07</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>99361.64999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>35612.89</v>
+        <v>974721.99</v>
       </c>
       <c r="J52" t="n">
-        <v>35612.89</v>
+        <v>1074083.64</v>
       </c>
     </row>
     <row r="53">
@@ -2310,34 +2298,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1915</v>
+        <v>2041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>77370454.08</v>
+        <v>2753285.11</v>
       </c>
       <c r="F53" t="n">
-        <v>77346508.56999999</v>
+        <v>2718960.43</v>
       </c>
       <c r="G53" t="n">
-        <v>77346508.56999999</v>
+        <v>2712294.25</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>259334068.7</v>
+        <v>52615.45</v>
       </c>
       <c r="J53" t="n">
-        <v>259334068.7</v>
+        <v>52615.45</v>
       </c>
     </row>
     <row r="54">
@@ -2346,34 +2334,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1511</v>
+        <v>1101</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2971107807.85</v>
+        <v>16775084.75</v>
       </c>
       <c r="F54" t="n">
-        <v>2911787285.47</v>
+        <v>16686029.56</v>
       </c>
       <c r="G54" t="n">
-        <v>2882948197.58</v>
+        <v>16501107.08</v>
       </c>
       <c r="H54" t="n">
-        <v>6144267.39</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>64134975.09</v>
+        <v>35612.89</v>
       </c>
       <c r="J54" t="n">
-        <v>70279242.48</v>
+        <v>35612.89</v>
       </c>
     </row>
     <row r="55">
@@ -2382,34 +2370,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1251</v>
+        <v>1915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>14358949915.03</v>
+        <v>77370454.08</v>
       </c>
       <c r="F55" t="n">
-        <v>14172994593.1</v>
+        <v>77346508.56999999</v>
       </c>
       <c r="G55" t="n">
-        <v>14136708514.63</v>
+        <v>77346508.56999999</v>
       </c>
       <c r="H55" t="n">
-        <v>25047110.83</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>200233686.02</v>
+        <v>259334068.7</v>
       </c>
       <c r="J55" t="n">
-        <v>225280796.85</v>
+        <v>259334068.7</v>
       </c>
     </row>
     <row r="56">
@@ -2418,34 +2406,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1721</v>
+        <v>1511</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>11376822.58</v>
+        <v>2971107807.85</v>
       </c>
       <c r="F56" t="n">
-        <v>10825343.53</v>
+        <v>2911787285.47</v>
       </c>
       <c r="G56" t="n">
-        <v>10646102.96</v>
+        <v>2882948197.58</v>
       </c>
       <c r="H56" t="n">
-        <v>256630.64</v>
+        <v>6144267.39</v>
       </c>
       <c r="I56" t="n">
-        <v>226579.48</v>
+        <v>64134975.09</v>
       </c>
       <c r="J56" t="n">
-        <v>483210.12</v>
+        <v>70279242.48</v>
       </c>
     </row>
     <row r="57">
@@ -2454,34 +2442,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>144310208.36</v>
+        <v>14358949915.03</v>
       </c>
       <c r="F57" t="n">
-        <v>121768607.78</v>
+        <v>14172994593.1</v>
       </c>
       <c r="G57" t="n">
-        <v>115667927.76</v>
+        <v>14136708514.63</v>
       </c>
       <c r="H57" t="n">
-        <v>16655601.21</v>
+        <v>25047110.83</v>
       </c>
       <c r="I57" t="n">
-        <v>13370006.41</v>
+        <v>200233686.02</v>
       </c>
       <c r="J57" t="n">
-        <v>30025607.62</v>
+        <v>225280796.85</v>
       </c>
     </row>
     <row r="58">
@@ -2490,34 +2478,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1631</v>
+        <v>1721</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9422516.710000001</v>
+        <v>11376822.58</v>
       </c>
       <c r="F58" t="n">
-        <v>9269804.6</v>
+        <v>10825343.53</v>
       </c>
       <c r="G58" t="n">
-        <v>9157892.960000001</v>
+        <v>10646102.96</v>
       </c>
       <c r="H58" t="n">
-        <v>7873.12</v>
+        <v>256630.64</v>
       </c>
       <c r="I58" t="n">
-        <v>3228098.93</v>
+        <v>226579.48</v>
       </c>
       <c r="J58" t="n">
-        <v>3235972.05</v>
+        <v>483210.12</v>
       </c>
     </row>
     <row r="59">
@@ -2526,34 +2514,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1711</v>
+        <v>1231</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>145415971.84</v>
+        <v>144310208.36</v>
       </c>
       <c r="F59" t="n">
-        <v>57212986.34</v>
+        <v>121768607.78</v>
       </c>
       <c r="G59" t="n">
-        <v>54811118.27</v>
+        <v>115667927.76</v>
       </c>
       <c r="H59" t="n">
-        <v>13711.91</v>
+        <v>16655601.21</v>
       </c>
       <c r="I59" t="n">
-        <v>45385504.04</v>
+        <v>13370006.41</v>
       </c>
       <c r="J59" t="n">
-        <v>45399215.95</v>
+        <v>30025607.62</v>
       </c>
     </row>
     <row r="60">
@@ -2562,34 +2550,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1271</v>
+        <v>1631</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>278574229.65</v>
+        <v>9422516.710000001</v>
       </c>
       <c r="F60" t="n">
-        <v>275244209.69</v>
+        <v>9269804.6</v>
       </c>
       <c r="G60" t="n">
-        <v>272306597.26</v>
+        <v>9157892.960000001</v>
       </c>
       <c r="H60" t="n">
-        <v>2848477.47</v>
+        <v>7873.12</v>
       </c>
       <c r="I60" t="n">
-        <v>1058475.57</v>
+        <v>3228098.93</v>
       </c>
       <c r="J60" t="n">
-        <v>3906953.04</v>
+        <v>3235972.05</v>
       </c>
     </row>
     <row r="61">
@@ -2598,34 +2586,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1221</v>
+        <v>1711</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>73450042.36</v>
+        <v>145415971.84</v>
       </c>
       <c r="F61" t="n">
-        <v>68755382.68000001</v>
+        <v>57212986.34</v>
       </c>
       <c r="G61" t="n">
-        <v>67360741.43000001</v>
+        <v>54811118.27</v>
       </c>
       <c r="H61" t="n">
-        <v>20159858.67</v>
+        <v>13711.91</v>
       </c>
       <c r="I61" t="n">
-        <v>2093275.95</v>
+        <v>45385504.04</v>
       </c>
       <c r="J61" t="n">
-        <v>22253134.62</v>
+        <v>45399215.95</v>
       </c>
     </row>
     <row r="62">
@@ -2634,34 +2622,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1481</v>
+        <v>1271</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>192351891.57</v>
+        <v>278574229.65</v>
       </c>
       <c r="F62" t="n">
-        <v>161820266.28</v>
+        <v>275244209.69</v>
       </c>
       <c r="G62" t="n">
-        <v>151442671.16</v>
+        <v>272306597.26</v>
       </c>
       <c r="H62" t="n">
-        <v>69047832.11</v>
+        <v>2848477.47</v>
       </c>
       <c r="I62" t="n">
-        <v>5228463.57</v>
+        <v>1058475.57</v>
       </c>
       <c r="J62" t="n">
-        <v>74276295.68000001</v>
+        <v>3906953.04</v>
       </c>
     </row>
     <row r="63">
@@ -2670,34 +2658,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>19265871510.98</v>
+        <v>73450042.36</v>
       </c>
       <c r="F63" t="n">
-        <v>18803285393.11</v>
+        <v>68755382.68000001</v>
       </c>
       <c r="G63" t="n">
-        <v>18714498875.1</v>
+        <v>67360741.43000001</v>
       </c>
       <c r="H63" t="n">
-        <v>270741595.99</v>
+        <v>20159858.67</v>
       </c>
       <c r="I63" t="n">
-        <v>353672915.64</v>
+        <v>2093275.95</v>
       </c>
       <c r="J63" t="n">
-        <v>624414511.63</v>
+        <v>22253134.62</v>
       </c>
     </row>
     <row r="64">
@@ -2706,34 +2694,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1191</v>
+        <v>1481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1774005537.77</v>
+        <v>192351891.57</v>
       </c>
       <c r="F64" t="n">
-        <v>1675743095.87</v>
+        <v>161820266.28</v>
       </c>
       <c r="G64" t="n">
-        <v>1655219211.46</v>
+        <v>151442671.16</v>
       </c>
       <c r="H64" t="n">
-        <v>9452783.43</v>
+        <v>69047832.11</v>
       </c>
       <c r="I64" t="n">
-        <v>44016084.48</v>
+        <v>5228463.57</v>
       </c>
       <c r="J64" t="n">
-        <v>53468867.91</v>
+        <v>74276295.68000001</v>
       </c>
     </row>
     <row r="65">
@@ -2742,34 +2730,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1491</v>
+        <v>1261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>936918721.67</v>
+        <v>19265871510.98</v>
       </c>
       <c r="F65" t="n">
-        <v>903588865.71</v>
+        <v>18803285393.11</v>
       </c>
       <c r="G65" t="n">
-        <v>899254287.64</v>
+        <v>18714498875.1</v>
       </c>
       <c r="H65" t="n">
-        <v>2218245.96</v>
+        <v>270741595.99</v>
       </c>
       <c r="I65" t="n">
-        <v>40834360.64</v>
+        <v>353672915.64</v>
       </c>
       <c r="J65" t="n">
-        <v>43052606.6</v>
+        <v>624414511.63</v>
       </c>
     </row>
     <row r="66">
@@ -2778,34 +2766,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>739415330.3099999</v>
+        <v>1774005537.77</v>
       </c>
       <c r="F66" t="n">
-        <v>535038118.5</v>
+        <v>1675743095.87</v>
       </c>
       <c r="G66" t="n">
-        <v>520804921.24</v>
+        <v>1655219211.46</v>
       </c>
       <c r="H66" t="n">
-        <v>79602772.47</v>
+        <v>9452783.43</v>
       </c>
       <c r="I66" t="n">
-        <v>79301096.69</v>
+        <v>44016084.48</v>
       </c>
       <c r="J66" t="n">
-        <v>158903869.16</v>
+        <v>53468867.91</v>
       </c>
     </row>
     <row r="67">
@@ -2814,34 +2802,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4151305223.12</v>
+        <v>936918721.67</v>
       </c>
       <c r="F67" t="n">
-        <v>4013226715.05</v>
+        <v>903588865.71</v>
       </c>
       <c r="G67" t="n">
-        <v>3984233963.53</v>
+        <v>899254287.64</v>
       </c>
       <c r="H67" t="n">
-        <v>16641871.41</v>
+        <v>2218245.96</v>
       </c>
       <c r="I67" t="n">
-        <v>126747618.81</v>
+        <v>40834360.64</v>
       </c>
       <c r="J67" t="n">
-        <v>143389490.22</v>
+        <v>43052606.6</v>
       </c>
     </row>
     <row r="68">
@@ -2850,34 +2838,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>184730264.23</v>
+        <v>739415330.3099999</v>
       </c>
       <c r="F68" t="n">
-        <v>174620059.85</v>
+        <v>535038118.5</v>
       </c>
       <c r="G68" t="n">
-        <v>171768182.39</v>
+        <v>520804921.24</v>
       </c>
       <c r="H68" t="n">
-        <v>16148951.81</v>
+        <v>79602772.47</v>
       </c>
       <c r="I68" t="n">
-        <v>3698488.6</v>
+        <v>79301096.69</v>
       </c>
       <c r="J68" t="n">
-        <v>19847440.41</v>
+        <v>158903869.16</v>
       </c>
     </row>
     <row r="69">
@@ -2886,34 +2874,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>855546794.0599999</v>
+        <v>4151305223.12</v>
       </c>
       <c r="F69" t="n">
-        <v>760671962.17</v>
+        <v>4013226715.05</v>
       </c>
       <c r="G69" t="n">
-        <v>719982759.6799999</v>
+        <v>3984233963.53</v>
       </c>
       <c r="H69" t="n">
-        <v>10865754.29</v>
+        <v>16641871.41</v>
       </c>
       <c r="I69" t="n">
-        <v>34522196.21</v>
+        <v>126747618.81</v>
       </c>
       <c r="J69" t="n">
-        <v>45387950.5</v>
+        <v>143389490.22</v>
       </c>
     </row>
     <row r="70">
@@ -2922,34 +2910,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2211</v>
+        <v>1371</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>18099484.14</v>
+        <v>184730264.23</v>
       </c>
       <c r="F70" t="n">
-        <v>16714066.1</v>
+        <v>174620059.85</v>
       </c>
       <c r="G70" t="n">
-        <v>15905442.44</v>
+        <v>171768182.39</v>
       </c>
       <c r="H70" t="n">
-        <v>333380.82</v>
+        <v>16148951.81</v>
       </c>
       <c r="I70" t="n">
-        <v>636002.17</v>
+        <v>3698488.6</v>
       </c>
       <c r="J70" t="n">
-        <v>969382.99</v>
+        <v>19847440.41</v>
       </c>
     </row>
     <row r="71">
@@ -2958,34 +2946,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2351</v>
+        <v>1501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>411019703.15</v>
+        <v>855546794.0599999</v>
       </c>
       <c r="F71" t="n">
-        <v>396207773.83</v>
+        <v>760671962.17</v>
       </c>
       <c r="G71" t="n">
-        <v>386312319.37</v>
+        <v>719982759.6799999</v>
       </c>
       <c r="H71" t="n">
-        <v>2944423.8</v>
+        <v>10865754.29</v>
       </c>
       <c r="I71" t="n">
-        <v>10470000.42</v>
+        <v>34522196.21</v>
       </c>
       <c r="J71" t="n">
-        <v>13414424.22</v>
+        <v>45387950.5</v>
       </c>
     </row>
     <row r="72">
@@ -2994,34 +2982,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2311</v>
+        <v>2211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>499332522.4</v>
+        <v>18099484.14</v>
       </c>
       <c r="F72" t="n">
-        <v>462442399.38</v>
+        <v>16714066.1</v>
       </c>
       <c r="G72" t="n">
-        <v>452206130.54</v>
+        <v>15905442.44</v>
       </c>
       <c r="H72" t="n">
-        <v>518698.7</v>
+        <v>333380.82</v>
       </c>
       <c r="I72" t="n">
-        <v>37770634.5</v>
+        <v>636002.17</v>
       </c>
       <c r="J72" t="n">
-        <v>38289333.2</v>
+        <v>969382.99</v>
       </c>
     </row>
     <row r="73">
@@ -3030,33 +3018,105 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>411019703.15</v>
+      </c>
+      <c r="F73" t="n">
+        <v>396207773.83</v>
+      </c>
+      <c r="G73" t="n">
+        <v>386312319.37</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2944423.8</v>
+      </c>
+      <c r="I73" t="n">
+        <v>10470000.42</v>
+      </c>
+      <c r="J73" t="n">
+        <v>13414424.22</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>499332522.4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>462442399.38</v>
+      </c>
+      <c r="G74" t="n">
+        <v>452206130.54</v>
+      </c>
+      <c r="H74" t="n">
+        <v>518698.7</v>
+      </c>
+      <c r="I74" t="n">
+        <v>37770634.5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>38289333.2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C75" t="n">
         <v>2281</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E75" t="n">
         <v>6571067.71</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F75" t="n">
         <v>6006116.69</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G75" t="n">
         <v>5621531.59</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H75" t="n">
         <v>10063.62</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I75" t="n">
         <v>209239.25</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J75" t="n">
         <v>219302.87</v>
       </c>
     </row>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,34 +558,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARMVA</t>
+          <t>ALMG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2461</v>
+        <v>1011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4028221.25</v>
+        <v>1993348129.81</v>
       </c>
       <c r="F4" t="n">
-        <v>3832188.55</v>
+        <v>1953917585.32</v>
       </c>
       <c r="G4" t="n">
-        <v>3637560.66</v>
+        <v>1979843435.94</v>
       </c>
       <c r="H4" t="n">
-        <v>313892.1</v>
+        <v>2701.16</v>
       </c>
       <c r="I4" t="n">
-        <v>708121.74</v>
+        <v>28865173.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1022013.84</v>
+        <v>28867874.96</v>
       </c>
     </row>
     <row r="5">
@@ -594,34 +594,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARSAE -MG</t>
+          <t>ARMVA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2441</v>
+        <v>2461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18320816.57</v>
+        <v>4028221.25</v>
       </c>
       <c r="F5" t="n">
-        <v>17901288.28</v>
+        <v>3832188.55</v>
       </c>
       <c r="G5" t="n">
-        <v>17655954.74</v>
+        <v>3637560.66</v>
       </c>
       <c r="H5" t="n">
-        <v>151.04</v>
+        <v>313892.1</v>
       </c>
       <c r="I5" t="n">
-        <v>617418.72</v>
+        <v>708121.74</v>
       </c>
       <c r="J5" t="n">
-        <v>617569.76</v>
+        <v>1022013.84</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CBMMG</t>
+          <t>ARSAE -MG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1401</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1689247203.39</v>
+        <v>18320816.57</v>
       </c>
       <c r="F6" t="n">
-        <v>1633624349.86</v>
+        <v>17901288.28</v>
       </c>
       <c r="G6" t="n">
-        <v>1628884534.15</v>
+        <v>17655954.74</v>
       </c>
       <c r="H6" t="n">
-        <v>6962587.39</v>
+        <v>151.04</v>
       </c>
       <c r="I6" t="n">
-        <v>71853078.97</v>
+        <v>617418.72</v>
       </c>
       <c r="J6" t="n">
-        <v>78815666.36</v>
+        <v>617569.76</v>
       </c>
     </row>
     <row r="7">
@@ -666,34 +666,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CGE</t>
+          <t>CBMMG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1521</v>
+        <v>1401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CONTROLADORIA-GERAL DO ESTADO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67525357.7</v>
+        <v>1689247203.39</v>
       </c>
       <c r="F7" t="n">
-        <v>66249891.55</v>
+        <v>1633624349.86</v>
       </c>
       <c r="G7" t="n">
-        <v>66020996.24</v>
+        <v>1628884534.15</v>
       </c>
       <c r="H7" t="n">
-        <v>96745.82000000001</v>
+        <v>6962587.39</v>
       </c>
       <c r="I7" t="n">
-        <v>487607.59</v>
+        <v>71853078.97</v>
       </c>
       <c r="J7" t="n">
-        <v>584353.41</v>
+        <v>78815666.36</v>
       </c>
     </row>
     <row r="8">
@@ -702,34 +702,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DER-MG</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2301</v>
+        <v>1521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>CONTROLADORIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2166907648.97</v>
+        <v>67525357.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1614406418.07</v>
+        <v>66249891.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1579074300.12</v>
+        <v>66020996.24</v>
       </c>
       <c r="H8" t="n">
-        <v>36034587.04</v>
+        <v>96745.82000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>372221350.62</v>
+        <v>487607.59</v>
       </c>
       <c r="J8" t="n">
-        <v>408255937.66</v>
+        <v>584353.41</v>
       </c>
     </row>
     <row r="9">
@@ -738,34 +738,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EGE - SEF</t>
+          <t>DEF PUB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1911</v>
+        <v>1441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1542024334.18</v>
+        <v>970482007.65</v>
       </c>
       <c r="F9" t="n">
-        <v>1424388867.28</v>
+        <v>943462655.92</v>
       </c>
       <c r="G9" t="n">
-        <v>1424388867.28</v>
+        <v>933984191.4</v>
       </c>
       <c r="H9" t="n">
-        <v>23280.48</v>
+        <v>22329.81</v>
       </c>
       <c r="I9" t="n">
-        <v>58649930.03</v>
+        <v>21975000.91</v>
       </c>
       <c r="J9" t="n">
-        <v>58673210.51</v>
+        <v>21997330.72</v>
       </c>
     </row>
     <row r="10">
@@ -774,34 +774,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EGE-SEPLAG</t>
+          <t>DER-MG</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1941</v>
+        <v>2301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>198068287.51</v>
+        <v>2166907648.97</v>
       </c>
       <c r="F10" t="n">
-        <v>195102654.49</v>
+        <v>1614406418.07</v>
       </c>
       <c r="G10" t="n">
-        <v>195045661.81</v>
+        <v>1579074300.12</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>36034587.04</v>
       </c>
       <c r="I10" t="n">
-        <v>306318.7</v>
+        <v>372221350.62</v>
       </c>
       <c r="J10" t="n">
-        <v>306318.7</v>
+        <v>408255937.66</v>
       </c>
     </row>
     <row r="11">
@@ -810,29 +810,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>EGE - SEF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3041</v>
+        <v>1911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>399961543.69</v>
+        <v>1542024334.18</v>
       </c>
       <c r="F11" t="n">
-        <v>399961543.69</v>
+        <v>1424388867.28</v>
       </c>
       <c r="G11" t="n">
-        <v>399961543.69</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>1424388867.28</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23280.48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>58649930.03</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58673210.51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -840,29 +846,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>EGE-SEPLAG</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3151</v>
+        <v>1941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>29599261.39</v>
+        <v>198068287.51</v>
       </c>
       <c r="F12" t="n">
-        <v>29599261.39</v>
+        <v>195102654.49</v>
       </c>
       <c r="G12" t="n">
-        <v>29599261.39</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>195045661.81</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>306318.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>306318.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -870,25 +882,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3051</v>
+        <v>3041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>135695037.88</v>
+        <v>399961543.69</v>
       </c>
       <c r="F13" t="n">
-        <v>135695037.88</v>
+        <v>399961543.69</v>
       </c>
       <c r="G13" t="n">
-        <v>135695037.88</v>
+        <v>399961543.69</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -900,35 +912,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1541</v>
+        <v>3151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21259443.36</v>
+        <v>29599261.39</v>
       </c>
       <c r="F14" t="n">
-        <v>20594781.94</v>
+        <v>29599261.39</v>
       </c>
       <c r="G14" t="n">
-        <v>20198969.09</v>
-      </c>
-      <c r="H14" t="n">
-        <v>11884.85</v>
-      </c>
-      <c r="I14" t="n">
-        <v>215304.71</v>
-      </c>
-      <c r="J14" t="n">
-        <v>227189.56</v>
-      </c>
+        <v>29599261.39</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -936,35 +942,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4541</v>
+        <v>3051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>391438.2</v>
+        <v>135695037.88</v>
       </c>
       <c r="F15" t="n">
-        <v>305805.64</v>
+        <v>135695037.88</v>
       </c>
       <c r="G15" t="n">
-        <v>288797.79</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>26155.45</v>
-      </c>
-      <c r="J15" t="n">
-        <v>26155.45</v>
-      </c>
+        <v>135695037.88</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,34 +972,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2171</v>
+        <v>1541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7941833.37</v>
+        <v>21259443.36</v>
       </c>
       <c r="F16" t="n">
-        <v>7516887.29</v>
+        <v>20594781.94</v>
       </c>
       <c r="G16" t="n">
-        <v>6813631.04</v>
+        <v>20198969.09</v>
       </c>
       <c r="H16" t="n">
-        <v>55347.98</v>
+        <v>11884.85</v>
       </c>
       <c r="I16" t="n">
-        <v>249487.78</v>
+        <v>215304.71</v>
       </c>
       <c r="J16" t="n">
-        <v>304835.76</v>
+        <v>227189.56</v>
       </c>
     </row>
     <row r="17">
@@ -1008,34 +1008,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2071</v>
+        <v>4541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>533594583.23</v>
+        <v>391438.2</v>
       </c>
       <c r="F17" t="n">
-        <v>523602791.54</v>
+        <v>305805.64</v>
       </c>
       <c r="G17" t="n">
-        <v>524266165.17</v>
+        <v>288797.79</v>
       </c>
       <c r="H17" t="n">
-        <v>46197437.79</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>5632677.28</v>
+        <v>26155.45</v>
       </c>
       <c r="J17" t="n">
-        <v>51830115.07</v>
+        <v>26155.45</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +1044,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>61200638.61</v>
+        <v>7941833.37</v>
       </c>
       <c r="F18" t="n">
-        <v>58218035.71</v>
+        <v>7516887.29</v>
       </c>
       <c r="G18" t="n">
-        <v>55031527.64</v>
+        <v>6813631.04</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>55347.98</v>
       </c>
       <c r="I18" t="n">
-        <v>1781014.41</v>
+        <v>249487.78</v>
       </c>
       <c r="J18" t="n">
-        <v>1781014.41</v>
+        <v>304835.76</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1080,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4331</v>
+        <v>2071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1041559.94</v>
+        <v>533594583.23</v>
       </c>
       <c r="F19" t="n">
-        <v>823642.04</v>
+        <v>523602791.54</v>
       </c>
       <c r="G19" t="n">
-        <v>813093.72</v>
+        <v>524266165.17</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>46197437.79</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>5632677.28</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>51830115.07</v>
       </c>
     </row>
     <row r="20">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2091</v>
+        <v>2181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>63780232.72</v>
+        <v>61200638.61</v>
       </c>
       <c r="F20" t="n">
-        <v>61454087.81</v>
+        <v>58218035.71</v>
       </c>
       <c r="G20" t="n">
-        <v>60658393.88</v>
+        <v>55031527.64</v>
       </c>
       <c r="H20" t="n">
-        <v>203832.51</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3314473.99</v>
+        <v>1781014.41</v>
       </c>
       <c r="J20" t="n">
-        <v>3518306.5</v>
+        <v>1781014.41</v>
       </c>
     </row>
     <row r="21">
@@ -1152,34 +1152,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4251</v>
+        <v>4331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>191504888.5</v>
+        <v>1041559.94</v>
       </c>
       <c r="F21" t="n">
-        <v>184497317.71</v>
+        <v>823642.04</v>
       </c>
       <c r="G21" t="n">
-        <v>182485356.67</v>
+        <v>813093.72</v>
       </c>
       <c r="H21" t="n">
-        <v>811297.6</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3954289.12</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4765586.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4491</v>
+        <v>2091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5173333.28</v>
+        <v>63780232.72</v>
       </c>
       <c r="F22" t="n">
-        <v>5153333.28</v>
+        <v>61454087.81</v>
       </c>
       <c r="G22" t="n">
-        <v>3822182.56</v>
+        <v>60658393.88</v>
       </c>
       <c r="H22" t="n">
-        <v>50000</v>
+        <v>203832.51</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3314473.99</v>
       </c>
       <c r="J22" t="n">
-        <v>50000</v>
+        <v>3518306.5</v>
       </c>
     </row>
     <row r="23">
@@ -1224,34 +1224,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4101</v>
+        <v>4251</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17635213.7</v>
+        <v>191504888.5</v>
       </c>
       <c r="F23" t="n">
-        <v>17616149.93</v>
+        <v>184497317.71</v>
       </c>
       <c r="G23" t="n">
-        <v>16185012.28</v>
+        <v>182485356.67</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>811297.6</v>
       </c>
       <c r="I23" t="n">
-        <v>130211.04</v>
+        <v>3954289.12</v>
       </c>
       <c r="J23" t="n">
-        <v>130211.04</v>
+        <v>4765586.72</v>
       </c>
     </row>
     <row r="24">
@@ -1260,34 +1260,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4601</v>
+        <v>4491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5060964</v>
+        <v>5173333.28</v>
       </c>
       <c r="F24" t="n">
-        <v>1670773.97</v>
+        <v>5153333.28</v>
       </c>
       <c r="G24" t="n">
-        <v>1595111.21</v>
+        <v>3822182.56</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="25">
@@ -1296,34 +1296,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4291</v>
+        <v>4101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11829504614.64</v>
+        <v>17635213.7</v>
       </c>
       <c r="F25" t="n">
-        <v>11406407458.04</v>
+        <v>17616149.93</v>
       </c>
       <c r="G25" t="n">
-        <v>11283113714.34</v>
+        <v>16185012.28</v>
       </c>
       <c r="H25" t="n">
-        <v>863891921.1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>625577799.01</v>
+        <v>130211.04</v>
       </c>
       <c r="J25" t="n">
-        <v>1489469720.11</v>
+        <v>130211.04</v>
       </c>
     </row>
     <row r="26">
@@ -1332,34 +1332,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4691</v>
+        <v>4601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49389640.21</v>
+        <v>5060964</v>
       </c>
       <c r="F26" t="n">
-        <v>15901164.57</v>
+        <v>1670773.97</v>
       </c>
       <c r="G26" t="n">
-        <v>13533037.66</v>
+        <v>1595111.21</v>
       </c>
       <c r="H26" t="n">
-        <v>1152378.09</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>44348538.92</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>45500917.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1368,34 +1368,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4701</v>
+        <v>4451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1242375.3</v>
+        <v>14312560.43</v>
       </c>
       <c r="F27" t="n">
-        <v>921616.21</v>
+        <v>8943123.68</v>
       </c>
       <c r="G27" t="n">
-        <v>921884.45</v>
+        <v>8217694.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4275.66</v>
+        <v>219306.4</v>
       </c>
       <c r="I27" t="n">
-        <v>446306.33</v>
+        <v>11388620.84</v>
       </c>
       <c r="J27" t="n">
-        <v>450581.99</v>
+        <v>11607927.24</v>
       </c>
     </row>
     <row r="28">
@@ -1404,34 +1404,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4711</v>
+        <v>4031</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17508957839.76</v>
+        <v>2274700897.5</v>
       </c>
       <c r="F28" t="n">
-        <v>17468843822.73</v>
+        <v>1956354064.55</v>
       </c>
       <c r="G28" t="n">
-        <v>17473304282.39</v>
+        <v>1765456359.42</v>
       </c>
       <c r="H28" t="n">
-        <v>11281.2</v>
+        <v>5636386.57</v>
       </c>
       <c r="I28" t="n">
-        <v>754605.42</v>
+        <v>162851696.69</v>
       </c>
       <c r="J28" t="n">
-        <v>765886.62</v>
+        <v>168488083.26</v>
       </c>
     </row>
     <row r="29">
@@ -1440,34 +1440,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2151</v>
+        <v>4291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>88180552.39</v>
+        <v>11829504614.64</v>
       </c>
       <c r="F29" t="n">
-        <v>80251235.98</v>
+        <v>11406407458.04</v>
       </c>
       <c r="G29" t="n">
-        <v>78333556.76000001</v>
+        <v>11283113714.34</v>
       </c>
       <c r="H29" t="n">
-        <v>16912.22</v>
+        <v>863891921.1</v>
       </c>
       <c r="I29" t="n">
-        <v>1852521.82</v>
+        <v>625577799.01</v>
       </c>
       <c r="J29" t="n">
-        <v>1869434.04</v>
+        <v>1489469720.11</v>
       </c>
     </row>
     <row r="30">
@@ -1476,34 +1476,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2271</v>
+        <v>4691</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2332862602.72</v>
+        <v>49389640.21</v>
       </c>
       <c r="F30" t="n">
-        <v>2250096399.41</v>
+        <v>15901164.57</v>
       </c>
       <c r="G30" t="n">
-        <v>2191298111.28</v>
+        <v>13533037.66</v>
       </c>
       <c r="H30" t="n">
-        <v>8172915.53</v>
+        <v>1152378.09</v>
       </c>
       <c r="I30" t="n">
-        <v>83039239.16</v>
+        <v>44348538.92</v>
       </c>
       <c r="J30" t="n">
-        <v>91212154.69</v>
+        <v>45500917.01</v>
       </c>
     </row>
     <row r="31">
@@ -1512,34 +1512,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4341</v>
+        <v>4701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4415220.16</v>
+        <v>1242375.3</v>
       </c>
       <c r="F31" t="n">
-        <v>3506542.63</v>
+        <v>921616.21</v>
       </c>
       <c r="G31" t="n">
-        <v>2790383.33</v>
+        <v>921884.45</v>
       </c>
       <c r="H31" t="n">
-        <v>183731.44</v>
+        <v>4275.66</v>
       </c>
       <c r="I31" t="n">
-        <v>384241.87</v>
+        <v>446306.33</v>
       </c>
       <c r="J31" t="n">
-        <v>567973.3100000001</v>
+        <v>450581.99</v>
       </c>
     </row>
     <row r="32">
@@ -1548,34 +1548,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4091</v>
+        <v>4711</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4781856.89</v>
+        <v>17508957839.76</v>
       </c>
       <c r="F32" t="n">
-        <v>1781856.89</v>
+        <v>17468843822.73</v>
       </c>
       <c r="G32" t="n">
-        <v>1780610.81</v>
+        <v>17473304282.39</v>
       </c>
       <c r="H32" t="n">
-        <v>1860786.86</v>
+        <v>11281.2</v>
       </c>
       <c r="I32" t="n">
-        <v>931646.02</v>
+        <v>754605.42</v>
       </c>
       <c r="J32" t="n">
-        <v>2792432.88</v>
+        <v>765886.62</v>
       </c>
     </row>
     <row r="33">
@@ -1584,34 +1584,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2061</v>
+        <v>2151</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>69147295.90000001</v>
+        <v>88180552.39</v>
       </c>
       <c r="F33" t="n">
-        <v>66097932.41</v>
+        <v>80251235.98</v>
       </c>
       <c r="G33" t="n">
-        <v>64809217.45</v>
+        <v>78333556.76000001</v>
       </c>
       <c r="H33" t="n">
-        <v>10992.51</v>
+        <v>16912.22</v>
       </c>
       <c r="I33" t="n">
-        <v>2944724.82</v>
+        <v>1852521.82</v>
       </c>
       <c r="J33" t="n">
-        <v>2955717.33</v>
+        <v>1869434.04</v>
       </c>
     </row>
     <row r="34">
@@ -1620,34 +1620,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4141</v>
+        <v>2271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32022766.9</v>
+        <v>2332862602.72</v>
       </c>
       <c r="F34" t="n">
-        <v>22913023.72</v>
+        <v>2250096399.41</v>
       </c>
       <c r="G34" t="n">
-        <v>22137652.86</v>
+        <v>2191298111.28</v>
       </c>
       <c r="H34" t="n">
-        <v>669506.88</v>
+        <v>8172915.53</v>
       </c>
       <c r="I34" t="n">
-        <v>4513043.66</v>
+        <v>83039239.16</v>
       </c>
       <c r="J34" t="n">
-        <v>5182550.54</v>
+        <v>91212154.69</v>
       </c>
     </row>
     <row r="35">
@@ -1656,34 +1656,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4631</v>
+        <v>4341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>497939201.43</v>
+        <v>4415220.16</v>
       </c>
       <c r="F35" t="n">
-        <v>379996046.23</v>
+        <v>3506542.63</v>
       </c>
       <c r="G35" t="n">
-        <v>356001665.76</v>
+        <v>2790383.33</v>
       </c>
       <c r="H35" t="n">
-        <v>6144215.84</v>
+        <v>183731.44</v>
       </c>
       <c r="I35" t="n">
-        <v>223775960.7</v>
+        <v>384241.87</v>
       </c>
       <c r="J35" t="n">
-        <v>229920176.54</v>
+        <v>567973.3100000001</v>
       </c>
     </row>
     <row r="36">
@@ -1692,34 +1692,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2161</v>
+        <v>4091</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8462182.16</v>
+        <v>4781856.89</v>
       </c>
       <c r="F36" t="n">
-        <v>7716382.45</v>
+        <v>1781856.89</v>
       </c>
       <c r="G36" t="n">
-        <v>7622126.71</v>
+        <v>1780610.81</v>
       </c>
       <c r="H36" t="n">
-        <v>256168.61</v>
+        <v>1860786.86</v>
       </c>
       <c r="I36" t="n">
-        <v>287975.89</v>
+        <v>931646.02</v>
       </c>
       <c r="J36" t="n">
-        <v>544144.5</v>
+        <v>2792432.88</v>
       </c>
     </row>
     <row r="37">
@@ -1728,34 +1728,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4551</v>
+        <v>2061</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>239438177.07</v>
+        <v>69147295.90000001</v>
       </c>
       <c r="F37" t="n">
-        <v>238618171.81</v>
+        <v>66097932.41</v>
       </c>
       <c r="G37" t="n">
-        <v>238609881.4</v>
+        <v>64809217.45</v>
       </c>
       <c r="H37" t="n">
-        <v>9732.950000000001</v>
+        <v>10992.51</v>
       </c>
       <c r="I37" t="n">
-        <v>1418075.3</v>
+        <v>2944724.82</v>
       </c>
       <c r="J37" t="n">
-        <v>1427808.25</v>
+        <v>2955717.33</v>
       </c>
     </row>
     <row r="38">
@@ -1764,29 +1764,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNDIF</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4421</v>
+        <v>4141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>490000</v>
+        <v>32022766.9</v>
       </c>
       <c r="F38" t="n">
-        <v>470895.13</v>
+        <v>22913023.72</v>
       </c>
       <c r="G38" t="n">
-        <v>470000</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+        <v>22137652.86</v>
+      </c>
+      <c r="H38" t="n">
+        <v>669506.88</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4513043.66</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5182550.54</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1794,34 +1800,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2261</v>
+        <v>4631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>617079458.6900001</v>
+        <v>497939201.43</v>
       </c>
       <c r="F39" t="n">
-        <v>457880133.86</v>
+        <v>379996046.23</v>
       </c>
       <c r="G39" t="n">
-        <v>414275548.19</v>
+        <v>356001665.76</v>
       </c>
       <c r="H39" t="n">
-        <v>915067.75</v>
+        <v>6144215.84</v>
       </c>
       <c r="I39" t="n">
-        <v>52633604.13</v>
+        <v>223775960.7</v>
       </c>
       <c r="J39" t="n">
-        <v>53548671.88</v>
+        <v>229920176.54</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1836,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4381</v>
+        <v>2161</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>121090271.58</v>
+        <v>8462182.16</v>
       </c>
       <c r="F40" t="n">
-        <v>82874506.28</v>
+        <v>7716382.45</v>
       </c>
       <c r="G40" t="n">
-        <v>79003714.81</v>
+        <v>7622126.71</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>256168.61</v>
       </c>
       <c r="I40" t="n">
-        <v>12075855.48</v>
+        <v>287975.89</v>
       </c>
       <c r="J40" t="n">
-        <v>12075855.48</v>
+        <v>544144.5</v>
       </c>
     </row>
     <row r="41">
@@ -1866,34 +1872,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1071</v>
+        <v>4551</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>39892772.32</v>
+        <v>239438177.07</v>
       </c>
       <c r="F41" t="n">
-        <v>35166360.52</v>
+        <v>238618171.81</v>
       </c>
       <c r="G41" t="n">
-        <v>34432753.31</v>
+        <v>238609881.4</v>
       </c>
       <c r="H41" t="n">
-        <v>630087.11</v>
+        <v>9732.950000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>7450507.6</v>
+        <v>1418075.3</v>
       </c>
       <c r="J41" t="n">
-        <v>8080594.71</v>
+        <v>1427808.25</v>
       </c>
     </row>
     <row r="42">
@@ -1902,34 +1908,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNDHAB</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1916</v>
+        <v>4121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3797673691.69</v>
+        <v>9244101.68</v>
       </c>
       <c r="F42" t="n">
-        <v>3797673691.69</v>
+        <v>8478581.68</v>
       </c>
       <c r="G42" t="n">
-        <v>3525271258.01</v>
+        <v>7748031.86</v>
       </c>
       <c r="H42" t="n">
-        <v>158424713.64</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>893205</v>
       </c>
       <c r="J42" t="n">
-        <v>158424713.64</v>
+        <v>893205</v>
       </c>
     </row>
     <row r="43">
@@ -1938,35 +1944,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2321</v>
+        <v>4421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>393216438.36</v>
+        <v>490000</v>
       </c>
       <c r="F43" t="n">
-        <v>350212418.49</v>
+        <v>470895.13</v>
       </c>
       <c r="G43" t="n">
-        <v>340044994.95</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1352290.48</v>
-      </c>
-      <c r="I43" t="n">
-        <v>28148241.67</v>
-      </c>
-      <c r="J43" t="n">
-        <v>29500532.15</v>
-      </c>
+        <v>470000</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1974,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2421</v>
+        <v>2261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53824647.21</v>
+        <v>617079458.6900001</v>
       </c>
       <c r="F44" t="n">
-        <v>33871287.27</v>
+        <v>457880133.86</v>
       </c>
       <c r="G44" t="n">
-        <v>32392034.26</v>
+        <v>414275548.19</v>
       </c>
       <c r="H44" t="n">
-        <v>656114.84</v>
+        <v>915067.75</v>
       </c>
       <c r="I44" t="n">
-        <v>7875523.48</v>
+        <v>52633604.13</v>
       </c>
       <c r="J44" t="n">
-        <v>8531638.32</v>
+        <v>53548671.88</v>
       </c>
     </row>
     <row r="45">
@@ -2010,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2101</v>
+        <v>4441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>217344980.62</v>
+        <v>21754563.35</v>
       </c>
       <c r="F45" t="n">
-        <v>207079100.46</v>
+        <v>12547861.55</v>
       </c>
       <c r="G45" t="n">
-        <v>198091936.58</v>
+        <v>12146604.86</v>
       </c>
       <c r="H45" t="n">
-        <v>521685.56</v>
+        <v>69519.91</v>
       </c>
       <c r="I45" t="n">
-        <v>4299011.63</v>
+        <v>17013291.39</v>
       </c>
       <c r="J45" t="n">
-        <v>4820697.19</v>
+        <v>17082811.3</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2201</v>
+        <v>4381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>32151361.8</v>
+        <v>121090271.58</v>
       </c>
       <c r="F46" t="n">
-        <v>29851278.47</v>
+        <v>82874506.28</v>
       </c>
       <c r="G46" t="n">
-        <v>27723914.95</v>
+        <v>79003714.81</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1740955.49</v>
+        <v>12075855.48</v>
       </c>
       <c r="J46" t="n">
-        <v>1740955.59</v>
+        <v>12075855.48</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2241</v>
+        <v>1071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>163783014.55</v>
+        <v>39892772.32</v>
       </c>
       <c r="F47" t="n">
-        <v>159345489.81</v>
+        <v>35166360.52</v>
       </c>
       <c r="G47" t="n">
-        <v>158705842.44</v>
+        <v>34432753.31</v>
       </c>
       <c r="H47" t="n">
-        <v>28637714.75</v>
+        <v>630087.11</v>
       </c>
       <c r="I47" t="n">
-        <v>1953947.48</v>
+        <v>7450507.6</v>
       </c>
       <c r="J47" t="n">
-        <v>30591662.23</v>
+        <v>8080594.71</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2371</v>
+        <v>1916</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>281022284.81</v>
+        <v>3797673691.69</v>
       </c>
       <c r="F48" t="n">
-        <v>272651863.28</v>
+        <v>3797673691.69</v>
       </c>
       <c r="G48" t="n">
-        <v>271364090.09</v>
+        <v>3525271258.01</v>
       </c>
       <c r="H48" t="n">
-        <v>21502.46</v>
+        <v>158424713.64</v>
       </c>
       <c r="I48" t="n">
-        <v>3360355.35</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>3381857.81</v>
+        <v>158424713.64</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2331</v>
+        <v>2321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33811040.59</v>
+        <v>393216438.36</v>
       </c>
       <c r="F49" t="n">
-        <v>33218643.65</v>
+        <v>350212418.49</v>
       </c>
       <c r="G49" t="n">
-        <v>31654005.09</v>
+        <v>340044994.95</v>
       </c>
       <c r="H49" t="n">
-        <v>519444.53</v>
+        <v>1352290.48</v>
       </c>
       <c r="I49" t="n">
-        <v>471410.62</v>
+        <v>28148241.67</v>
       </c>
       <c r="J49" t="n">
-        <v>990855.15</v>
+        <v>29500532.15</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2011</v>
+        <v>2421</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1725474955.8</v>
+        <v>53824647.21</v>
       </c>
       <c r="F50" t="n">
-        <v>1598962422.88</v>
+        <v>33871287.27</v>
       </c>
       <c r="G50" t="n">
-        <v>1555299505.74</v>
+        <v>32392034.26</v>
       </c>
       <c r="H50" t="n">
-        <v>1217572.7</v>
+        <v>656114.84</v>
       </c>
       <c r="I50" t="n">
-        <v>166587616.35</v>
+        <v>7875523.48</v>
       </c>
       <c r="J50" t="n">
-        <v>167805189.05</v>
+        <v>8531638.32</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3010650321.59</v>
+        <v>217344980.62</v>
       </c>
       <c r="F51" t="n">
-        <v>2990182081.12</v>
+        <v>207079100.46</v>
       </c>
       <c r="G51" t="n">
-        <v>2961013745.75</v>
+        <v>198091936.58</v>
       </c>
       <c r="H51" t="n">
-        <v>70175211.91</v>
+        <v>521685.56</v>
       </c>
       <c r="I51" t="n">
-        <v>12134894.13</v>
+        <v>4299011.63</v>
       </c>
       <c r="J51" t="n">
-        <v>82310106.04000001</v>
+        <v>4820697.19</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2251</v>
+        <v>2201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>34101030</v>
+        <v>32151361.8</v>
       </c>
       <c r="F52" t="n">
-        <v>32049801.81</v>
+        <v>29851278.47</v>
       </c>
       <c r="G52" t="n">
-        <v>31364550.07</v>
+        <v>27723914.95</v>
       </c>
       <c r="H52" t="n">
-        <v>99361.64999999999</v>
+        <v>0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>974721.99</v>
+        <v>1740955.49</v>
       </c>
       <c r="J52" t="n">
-        <v>1074083.64</v>
+        <v>1740955.59</v>
       </c>
     </row>
     <row r="53">
@@ -2298,34 +2298,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2041</v>
+        <v>2241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2753285.11</v>
+        <v>163783014.55</v>
       </c>
       <c r="F53" t="n">
-        <v>2718960.43</v>
+        <v>159345489.81</v>
       </c>
       <c r="G53" t="n">
-        <v>2712294.25</v>
+        <v>158705842.44</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>28637714.75</v>
       </c>
       <c r="I53" t="n">
-        <v>52615.45</v>
+        <v>1953947.48</v>
       </c>
       <c r="J53" t="n">
-        <v>52615.45</v>
+        <v>30591662.23</v>
       </c>
     </row>
     <row r="54">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1101</v>
+        <v>2371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>16775084.75</v>
+        <v>281022284.81</v>
       </c>
       <c r="F54" t="n">
-        <v>16686029.56</v>
+        <v>272651863.28</v>
       </c>
       <c r="G54" t="n">
-        <v>16501107.08</v>
+        <v>271364090.09</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>21502.46</v>
       </c>
       <c r="I54" t="n">
-        <v>35612.89</v>
+        <v>3360355.35</v>
       </c>
       <c r="J54" t="n">
-        <v>35612.89</v>
+        <v>3381857.81</v>
       </c>
     </row>
     <row r="55">
@@ -2370,34 +2370,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1915</v>
+        <v>2331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>77370454.08</v>
+        <v>33811040.59</v>
       </c>
       <c r="F55" t="n">
-        <v>77346508.56999999</v>
+        <v>33218643.65</v>
       </c>
       <c r="G55" t="n">
-        <v>77346508.56999999</v>
+        <v>31654005.09</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>519444.53</v>
       </c>
       <c r="I55" t="n">
-        <v>259334068.7</v>
+        <v>471410.62</v>
       </c>
       <c r="J55" t="n">
-        <v>259334068.7</v>
+        <v>990855.15</v>
       </c>
     </row>
     <row r="56">
@@ -2406,35 +2406,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1511</v>
+        <v>2361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2971107807.85</v>
+        <v>66040115.72</v>
       </c>
       <c r="F56" t="n">
-        <v>2911787285.47</v>
+        <v>66040115.72</v>
       </c>
       <c r="G56" t="n">
-        <v>2882948197.58</v>
-      </c>
-      <c r="H56" t="n">
-        <v>6144267.39</v>
-      </c>
-      <c r="I56" t="n">
-        <v>64134975.09</v>
-      </c>
-      <c r="J56" t="n">
-        <v>70279242.48</v>
-      </c>
+        <v>66040115.72</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2442,34 +2436,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1251</v>
+        <v>2011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>14358949915.03</v>
+        <v>1725474955.8</v>
       </c>
       <c r="F57" t="n">
-        <v>14172994593.1</v>
+        <v>1598962422.88</v>
       </c>
       <c r="G57" t="n">
-        <v>14136708514.63</v>
+        <v>1555299505.74</v>
       </c>
       <c r="H57" t="n">
-        <v>25047110.83</v>
+        <v>1217572.7</v>
       </c>
       <c r="I57" t="n">
-        <v>200233686.02</v>
+        <v>166587616.35</v>
       </c>
       <c r="J57" t="n">
-        <v>225280796.85</v>
+        <v>167805189.05</v>
       </c>
     </row>
     <row r="58">
@@ -2478,34 +2472,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1721</v>
+        <v>2121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11376822.58</v>
+        <v>3010650321.59</v>
       </c>
       <c r="F58" t="n">
-        <v>10825343.53</v>
+        <v>2990182081.12</v>
       </c>
       <c r="G58" t="n">
-        <v>10646102.96</v>
+        <v>2961013745.75</v>
       </c>
       <c r="H58" t="n">
-        <v>256630.64</v>
+        <v>70175211.91</v>
       </c>
       <c r="I58" t="n">
-        <v>226579.48</v>
+        <v>12134894.13</v>
       </c>
       <c r="J58" t="n">
-        <v>483210.12</v>
+        <v>82310106.04000001</v>
       </c>
     </row>
     <row r="59">
@@ -2514,34 +2508,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1231</v>
+        <v>2251</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>144310208.36</v>
+        <v>34101030</v>
       </c>
       <c r="F59" t="n">
-        <v>121768607.78</v>
+        <v>32049801.81</v>
       </c>
       <c r="G59" t="n">
-        <v>115667927.76</v>
+        <v>31364550.07</v>
       </c>
       <c r="H59" t="n">
-        <v>16655601.21</v>
+        <v>99361.64999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>13370006.41</v>
+        <v>974721.99</v>
       </c>
       <c r="J59" t="n">
-        <v>30025607.62</v>
+        <v>1074083.64</v>
       </c>
     </row>
     <row r="60">
@@ -2550,34 +2544,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1631</v>
+        <v>2041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>9422516.710000001</v>
+        <v>2753285.11</v>
       </c>
       <c r="F60" t="n">
-        <v>9269804.6</v>
+        <v>2718960.43</v>
       </c>
       <c r="G60" t="n">
-        <v>9157892.960000001</v>
+        <v>2712294.25</v>
       </c>
       <c r="H60" t="n">
-        <v>7873.12</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3228098.93</v>
+        <v>52615.45</v>
       </c>
       <c r="J60" t="n">
-        <v>3235972.05</v>
+        <v>52615.45</v>
       </c>
     </row>
     <row r="61">
@@ -2586,34 +2580,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1711</v>
+        <v>1101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>145415971.84</v>
+        <v>16775084.75</v>
       </c>
       <c r="F61" t="n">
-        <v>57212986.34</v>
+        <v>16686029.56</v>
       </c>
       <c r="G61" t="n">
-        <v>54811118.27</v>
+        <v>16501107.08</v>
       </c>
       <c r="H61" t="n">
-        <v>13711.91</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>45385504.04</v>
+        <v>35612.89</v>
       </c>
       <c r="J61" t="n">
-        <v>45399215.95</v>
+        <v>35612.89</v>
       </c>
     </row>
     <row r="62">
@@ -2622,34 +2616,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1271</v>
+        <v>1915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>278574229.65</v>
+        <v>77370454.08</v>
       </c>
       <c r="F62" t="n">
-        <v>275244209.69</v>
+        <v>77346508.56999999</v>
       </c>
       <c r="G62" t="n">
-        <v>272306597.26</v>
+        <v>77346508.56999999</v>
       </c>
       <c r="H62" t="n">
-        <v>2848477.47</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1058475.57</v>
+        <v>259334068.7</v>
       </c>
       <c r="J62" t="n">
-        <v>3906953.04</v>
+        <v>259334068.7</v>
       </c>
     </row>
     <row r="63">
@@ -2658,34 +2652,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1221</v>
+        <v>1511</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>73450042.36</v>
+        <v>2971107807.85</v>
       </c>
       <c r="F63" t="n">
-        <v>68755382.68000001</v>
+        <v>2911787285.47</v>
       </c>
       <c r="G63" t="n">
-        <v>67360741.43000001</v>
+        <v>2882948197.58</v>
       </c>
       <c r="H63" t="n">
-        <v>20159858.67</v>
+        <v>6144267.39</v>
       </c>
       <c r="I63" t="n">
-        <v>2093275.95</v>
+        <v>64134975.09</v>
       </c>
       <c r="J63" t="n">
-        <v>22253134.62</v>
+        <v>70279242.48</v>
       </c>
     </row>
     <row r="64">
@@ -2694,34 +2688,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1481</v>
+        <v>1091</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>192351891.57</v>
+        <v>3719366289.78</v>
       </c>
       <c r="F64" t="n">
-        <v>161820266.28</v>
+        <v>3595457252.17</v>
       </c>
       <c r="G64" t="n">
-        <v>151442671.16</v>
+        <v>3560537239.55</v>
       </c>
       <c r="H64" t="n">
-        <v>69047832.11</v>
+        <v>2972698.61</v>
       </c>
       <c r="I64" t="n">
-        <v>5228463.57</v>
+        <v>67746170.34</v>
       </c>
       <c r="J64" t="n">
-        <v>74276295.68000001</v>
+        <v>70718868.95</v>
       </c>
     </row>
     <row r="65">
@@ -2730,34 +2724,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>19265871510.98</v>
+        <v>14358949915.03</v>
       </c>
       <c r="F65" t="n">
-        <v>18803285393.11</v>
+        <v>14172994593.1</v>
       </c>
       <c r="G65" t="n">
-        <v>18714498875.1</v>
+        <v>14136708514.63</v>
       </c>
       <c r="H65" t="n">
-        <v>270741595.99</v>
+        <v>25047110.83</v>
       </c>
       <c r="I65" t="n">
-        <v>353672915.64</v>
+        <v>200233686.02</v>
       </c>
       <c r="J65" t="n">
-        <v>624414511.63</v>
+        <v>225280796.85</v>
       </c>
     </row>
     <row r="66">
@@ -2766,34 +2760,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1191</v>
+        <v>1721</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1774005537.77</v>
+        <v>11376822.58</v>
       </c>
       <c r="F66" t="n">
-        <v>1675743095.87</v>
+        <v>10825343.53</v>
       </c>
       <c r="G66" t="n">
-        <v>1655219211.46</v>
+        <v>10646102.96</v>
       </c>
       <c r="H66" t="n">
-        <v>9452783.43</v>
+        <v>256630.64</v>
       </c>
       <c r="I66" t="n">
-        <v>44016084.48</v>
+        <v>226579.48</v>
       </c>
       <c r="J66" t="n">
-        <v>53468867.91</v>
+        <v>483210.12</v>
       </c>
     </row>
     <row r="67">
@@ -2802,34 +2796,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1491</v>
+        <v>1231</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>936918721.67</v>
+        <v>144310208.36</v>
       </c>
       <c r="F67" t="n">
-        <v>903588865.71</v>
+        <v>121768607.78</v>
       </c>
       <c r="G67" t="n">
-        <v>899254287.64</v>
+        <v>115667927.76</v>
       </c>
       <c r="H67" t="n">
-        <v>2218245.96</v>
+        <v>16655601.21</v>
       </c>
       <c r="I67" t="n">
-        <v>40834360.64</v>
+        <v>13370006.41</v>
       </c>
       <c r="J67" t="n">
-        <v>43052606.6</v>
+        <v>30025607.62</v>
       </c>
     </row>
     <row r="68">
@@ -2838,34 +2832,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1301</v>
+        <v>1631</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>739415330.3099999</v>
+        <v>9422516.710000001</v>
       </c>
       <c r="F68" t="n">
-        <v>535038118.5</v>
+        <v>9269804.6</v>
       </c>
       <c r="G68" t="n">
-        <v>520804921.24</v>
+        <v>9157892.960000001</v>
       </c>
       <c r="H68" t="n">
-        <v>79602772.47</v>
+        <v>7873.12</v>
       </c>
       <c r="I68" t="n">
-        <v>79301096.69</v>
+        <v>3228098.93</v>
       </c>
       <c r="J68" t="n">
-        <v>158903869.16</v>
+        <v>3235972.05</v>
       </c>
     </row>
     <row r="69">
@@ -2874,34 +2868,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1451</v>
+        <v>1711</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4151305223.12</v>
+        <v>145415971.84</v>
       </c>
       <c r="F69" t="n">
-        <v>4013226715.05</v>
+        <v>57212986.34</v>
       </c>
       <c r="G69" t="n">
-        <v>3984233963.53</v>
+        <v>54811118.27</v>
       </c>
       <c r="H69" t="n">
-        <v>16641871.41</v>
+        <v>13711.91</v>
       </c>
       <c r="I69" t="n">
-        <v>126747618.81</v>
+        <v>45385504.04</v>
       </c>
       <c r="J69" t="n">
-        <v>143389490.22</v>
+        <v>45399215.95</v>
       </c>
     </row>
     <row r="70">
@@ -2910,34 +2904,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1371</v>
+        <v>1271</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>184730264.23</v>
+        <v>278574229.65</v>
       </c>
       <c r="F70" t="n">
-        <v>174620059.85</v>
+        <v>275244209.69</v>
       </c>
       <c r="G70" t="n">
-        <v>171768182.39</v>
+        <v>272306597.26</v>
       </c>
       <c r="H70" t="n">
-        <v>16148951.81</v>
+        <v>2848477.47</v>
       </c>
       <c r="I70" t="n">
-        <v>3698488.6</v>
+        <v>1058475.57</v>
       </c>
       <c r="J70" t="n">
-        <v>19847440.41</v>
+        <v>3906953.04</v>
       </c>
     </row>
     <row r="71">
@@ -2946,34 +2940,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1501</v>
+        <v>1221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>855546794.0599999</v>
+        <v>73450042.36</v>
       </c>
       <c r="F71" t="n">
-        <v>760671962.17</v>
+        <v>68755382.68000001</v>
       </c>
       <c r="G71" t="n">
-        <v>719982759.6799999</v>
+        <v>67360741.43000001</v>
       </c>
       <c r="H71" t="n">
-        <v>10865754.29</v>
+        <v>20159858.67</v>
       </c>
       <c r="I71" t="n">
-        <v>34522196.21</v>
+        <v>2093275.95</v>
       </c>
       <c r="J71" t="n">
-        <v>45387950.5</v>
+        <v>22253134.62</v>
       </c>
     </row>
     <row r="72">
@@ -2982,34 +2976,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2211</v>
+        <v>1481</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>18099484.14</v>
+        <v>192351891.57</v>
       </c>
       <c r="F72" t="n">
-        <v>16714066.1</v>
+        <v>161820266.28</v>
       </c>
       <c r="G72" t="n">
-        <v>15905442.44</v>
+        <v>151442671.16</v>
       </c>
       <c r="H72" t="n">
-        <v>333380.82</v>
+        <v>69047832.11</v>
       </c>
       <c r="I72" t="n">
-        <v>636002.17</v>
+        <v>5228463.57</v>
       </c>
       <c r="J72" t="n">
-        <v>969382.99</v>
+        <v>74276295.68000001</v>
       </c>
     </row>
     <row r="73">
@@ -3018,34 +3012,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2351</v>
+        <v>1261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>411019703.15</v>
+        <v>19265871510.98</v>
       </c>
       <c r="F73" t="n">
-        <v>396207773.83</v>
+        <v>18803285393.11</v>
       </c>
       <c r="G73" t="n">
-        <v>386312319.37</v>
+        <v>18714498875.1</v>
       </c>
       <c r="H73" t="n">
-        <v>2944423.8</v>
+        <v>270741595.99</v>
       </c>
       <c r="I73" t="n">
-        <v>10470000.42</v>
+        <v>353672915.64</v>
       </c>
       <c r="J73" t="n">
-        <v>13414424.22</v>
+        <v>624414511.63</v>
       </c>
     </row>
     <row r="74">
@@ -3054,34 +3048,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2311</v>
+        <v>1191</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>499332522.4</v>
+        <v>1774005537.77</v>
       </c>
       <c r="F74" t="n">
-        <v>462442399.38</v>
+        <v>1675743095.87</v>
       </c>
       <c r="G74" t="n">
-        <v>452206130.54</v>
+        <v>1655219211.46</v>
       </c>
       <c r="H74" t="n">
-        <v>518698.7</v>
+        <v>9452783.43</v>
       </c>
       <c r="I74" t="n">
-        <v>37770634.5</v>
+        <v>44016084.48</v>
       </c>
       <c r="J74" t="n">
-        <v>38289333.2</v>
+        <v>53468867.91</v>
       </c>
     </row>
     <row r="75">
@@ -3090,33 +3084,423 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>SEGOV</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>936918721.67</v>
+      </c>
+      <c r="F75" t="n">
+        <v>903588865.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>899254287.64</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2218245.96</v>
+      </c>
+      <c r="I75" t="n">
+        <v>40834360.64</v>
+      </c>
+      <c r="J75" t="n">
+        <v>43052606.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SEINFRA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>739415330.3099999</v>
+      </c>
+      <c r="F76" t="n">
+        <v>535038118.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>520804921.24</v>
+      </c>
+      <c r="H76" t="n">
+        <v>79602772.47</v>
+      </c>
+      <c r="I76" t="n">
+        <v>79301096.69</v>
+      </c>
+      <c r="J76" t="n">
+        <v>158903869.16</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SEJUSP</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4151305223.12</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4013226715.05</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3984233963.53</v>
+      </c>
+      <c r="H77" t="n">
+        <v>16641871.41</v>
+      </c>
+      <c r="I77" t="n">
+        <v>126747618.81</v>
+      </c>
+      <c r="J77" t="n">
+        <v>143389490.22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>184730264.23</v>
+      </c>
+      <c r="F78" t="n">
+        <v>174620059.85</v>
+      </c>
+      <c r="G78" t="n">
+        <v>171768182.39</v>
+      </c>
+      <c r="H78" t="n">
+        <v>16148951.81</v>
+      </c>
+      <c r="I78" t="n">
+        <v>3698488.6</v>
+      </c>
+      <c r="J78" t="n">
+        <v>19847440.41</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SEPLAG</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>855546794.0599999</v>
+      </c>
+      <c r="F79" t="n">
+        <v>760671962.17</v>
+      </c>
+      <c r="G79" t="n">
+        <v>719982759.6799999</v>
+      </c>
+      <c r="H79" t="n">
+        <v>10865754.29</v>
+      </c>
+      <c r="I79" t="n">
+        <v>34522196.21</v>
+      </c>
+      <c r="J79" t="n">
+        <v>45387950.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TCEMG</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1210662331.77</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1176050058.41</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1162004344.71</v>
+      </c>
+      <c r="H80" t="n">
+        <v>181476.44</v>
+      </c>
+      <c r="I80" t="n">
+        <v>15555853.23</v>
+      </c>
+      <c r="J80" t="n">
+        <v>15737329.67</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TJMG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>9337455728.58</v>
+      </c>
+      <c r="F81" t="n">
+        <v>9337455728.58</v>
+      </c>
+      <c r="G81" t="n">
+        <v>9337959841.530001</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TJMMG</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>136130325.04</v>
+      </c>
+      <c r="F82" t="n">
+        <v>130482064.44</v>
+      </c>
+      <c r="G82" t="n">
+        <v>129211193.82</v>
+      </c>
+      <c r="H82" t="n">
+        <v>191463.61</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3301434.56</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3492898.17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TV MINAS</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2211</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>18099484.14</v>
+      </c>
+      <c r="F83" t="n">
+        <v>16714066.1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>15905442.44</v>
+      </c>
+      <c r="H83" t="n">
+        <v>333380.82</v>
+      </c>
+      <c r="I83" t="n">
+        <v>636002.17</v>
+      </c>
+      <c r="J83" t="n">
+        <v>969382.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>411019703.15</v>
+      </c>
+      <c r="F84" t="n">
+        <v>396207773.83</v>
+      </c>
+      <c r="G84" t="n">
+        <v>386312319.37</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2944423.8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>10470000.42</v>
+      </c>
+      <c r="J84" t="n">
+        <v>13414424.22</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>499332522.4</v>
+      </c>
+      <c r="F85" t="n">
+        <v>462442399.38</v>
+      </c>
+      <c r="G85" t="n">
+        <v>452206130.54</v>
+      </c>
+      <c r="H85" t="n">
+        <v>518698.7</v>
+      </c>
+      <c r="I85" t="n">
+        <v>37770634.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>38289333.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C86" t="n">
         <v>2281</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E86" t="n">
         <v>6571067.71</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F86" t="n">
         <v>6006116.69</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G86" t="n">
         <v>5621531.59</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H86" t="n">
         <v>10063.62</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I86" t="n">
         <v>209239.25</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J86" t="n">
         <v>219302.87</v>
       </c>
     </row>

--- a/upload/orgao2024.xlsx
+++ b/upload/orgao2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,10 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Valor Pago Processado</t>
+          <t>Valor Liquidado RP</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Pago Não Processado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Pago RP</t>
         </is>
@@ -498,21 +493,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1176383140.29</v>
+        <v>29662044.89</v>
       </c>
       <c r="F2" t="n">
-        <v>1169049193.7</v>
+        <v>25057040.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1101390201.92</v>
+        <v>22393921.78</v>
       </c>
       <c r="H2" t="n">
-        <v>269694170.11</v>
+        <v>1437278.25</v>
       </c>
       <c r="I2" t="n">
-        <v>1347728.41</v>
-      </c>
-      <c r="J2" t="n">
         <v>271041898.52</v>
       </c>
     </row>
@@ -534,23 +526,20 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8106389.73</v>
+        <v>2854928.94</v>
       </c>
       <c r="F3" t="n">
-        <v>6808154.44</v>
+        <v>1580057.56</v>
       </c>
       <c r="G3" t="n">
-        <v>6635544.67</v>
+        <v>1407440.29</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>582262.25</v>
       </c>
       <c r="I3" t="n">
         <v>554251.7</v>
       </c>
-      <c r="J3" t="n">
-        <v>554251.7</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -570,21 +559,18 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1993348129.81</v>
+        <v>177371211.77</v>
       </c>
       <c r="F4" t="n">
-        <v>1953917585.32</v>
+        <v>142405450.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1979843435.94</v>
+        <v>129724899.14</v>
       </c>
       <c r="H4" t="n">
-        <v>2701.16</v>
+        <v>30501458.37</v>
       </c>
       <c r="I4" t="n">
-        <v>28865173.8</v>
-      </c>
-      <c r="J4" t="n">
         <v>28867874.96</v>
       </c>
     </row>
@@ -606,21 +592,18 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4028221.25</v>
+        <v>1712068.74</v>
       </c>
       <c r="F5" t="n">
-        <v>3832188.55</v>
+        <v>1534350.49</v>
       </c>
       <c r="G5" t="n">
-        <v>3637560.66</v>
+        <v>1339451.5</v>
       </c>
       <c r="H5" t="n">
-        <v>313892.1</v>
+        <v>718093.9399999999</v>
       </c>
       <c r="I5" t="n">
-        <v>708121.74</v>
-      </c>
-      <c r="J5" t="n">
         <v>1022013.84</v>
       </c>
     </row>
@@ -642,21 +625,18 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18320816.57</v>
+        <v>2240729.52</v>
       </c>
       <c r="F6" t="n">
-        <v>17901288.28</v>
+        <v>1859719.37</v>
       </c>
       <c r="G6" t="n">
-        <v>17655954.74</v>
+        <v>1612309.89</v>
       </c>
       <c r="H6" t="n">
-        <v>151.04</v>
+        <v>630228.48</v>
       </c>
       <c r="I6" t="n">
-        <v>617418.72</v>
-      </c>
-      <c r="J6" t="n">
         <v>617569.76</v>
       </c>
     </row>
@@ -678,21 +658,18 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1689247203.39</v>
+        <v>101796940.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1633624349.86</v>
+        <v>47689871.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1628884534.15</v>
+        <v>43243008.46</v>
       </c>
       <c r="H7" t="n">
-        <v>6962587.39</v>
+        <v>76195916.14</v>
       </c>
       <c r="I7" t="n">
-        <v>71853078.97</v>
-      </c>
-      <c r="J7" t="n">
         <v>78815666.36</v>
       </c>
     </row>
@@ -714,21 +691,18 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67525357.7</v>
+        <v>3276351.82</v>
       </c>
       <c r="F8" t="n">
-        <v>66249891.55</v>
+        <v>2072347.15</v>
       </c>
       <c r="G8" t="n">
-        <v>66020996.24</v>
+        <v>1837677.2</v>
       </c>
       <c r="H8" t="n">
-        <v>96745.82000000001</v>
+        <v>502975.55</v>
       </c>
       <c r="I8" t="n">
-        <v>487607.59</v>
-      </c>
-      <c r="J8" t="n">
         <v>584353.41</v>
       </c>
     </row>
@@ -750,21 +724,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>970482007.65</v>
+        <v>118915835.4</v>
       </c>
       <c r="F9" t="n">
-        <v>943462655.92</v>
+        <v>95589850.88</v>
       </c>
       <c r="G9" t="n">
-        <v>933984191.4</v>
+        <v>85786330.06999999</v>
       </c>
       <c r="H9" t="n">
-        <v>22329.81</v>
+        <v>23063957.08</v>
       </c>
       <c r="I9" t="n">
-        <v>21975000.91</v>
-      </c>
-      <c r="J9" t="n">
         <v>21997330.72</v>
       </c>
     </row>
@@ -786,21 +757,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2166907648.97</v>
+        <v>1739322604.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1614406418.07</v>
+        <v>1188097215.15</v>
       </c>
       <c r="G10" t="n">
-        <v>1579074300.12</v>
+        <v>1167599537.19</v>
       </c>
       <c r="H10" t="n">
-        <v>36034587.04</v>
+        <v>382313731.9</v>
       </c>
       <c r="I10" t="n">
-        <v>372221350.62</v>
-      </c>
-      <c r="J10" t="n">
         <v>408255937.66</v>
       </c>
     </row>
@@ -821,22 +789,13 @@
           <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1542024334.18</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1424388867.28</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1424388867.28</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>23280.48</v>
+        <v>58649930.03</v>
       </c>
       <c r="I11" t="n">
-        <v>58649930.03</v>
-      </c>
-      <c r="J11" t="n">
         <v>58673210.51</v>
       </c>
     </row>
@@ -858,23 +817,20 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>198068287.51</v>
+        <v>4148717.83</v>
       </c>
       <c r="F12" t="n">
-        <v>195102654.49</v>
+        <v>1183084.81</v>
       </c>
       <c r="G12" t="n">
-        <v>195045661.81</v>
+        <v>1126092.13</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>312023.12</v>
       </c>
       <c r="I12" t="n">
         <v>306318.7</v>
       </c>
-      <c r="J12" t="n">
-        <v>306318.7</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -904,7 +860,6 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -934,7 +889,6 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -942,29 +896,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMG - ADM. DIRETA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3051</v>
+        <v>9999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>135695037.88</v>
-      </c>
-      <c r="F15" t="n">
-        <v>135695037.88</v>
-      </c>
-      <c r="G15" t="n">
-        <v>135695037.88</v>
-      </c>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,35 +919,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21259443.36</v>
+        <v>135695037.88</v>
       </c>
       <c r="F16" t="n">
-        <v>20594781.94</v>
+        <v>135695037.88</v>
       </c>
       <c r="G16" t="n">
-        <v>20198969.09</v>
-      </c>
-      <c r="H16" t="n">
-        <v>11884.85</v>
-      </c>
-      <c r="I16" t="n">
-        <v>215304.71</v>
-      </c>
-      <c r="J16" t="n">
-        <v>227189.56</v>
-      </c>
+        <v>135695037.88</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1008,34 +948,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>391438.2</v>
+        <v>4776910.71</v>
       </c>
       <c r="F17" t="n">
-        <v>305805.64</v>
+        <v>4118099.23</v>
       </c>
       <c r="G17" t="n">
-        <v>288797.79</v>
+        <v>3723616.29</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>223988.18</v>
       </c>
       <c r="I17" t="n">
-        <v>26155.45</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26155.45</v>
+        <v>227189.56</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +981,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7941833.37</v>
+        <v>391438.2</v>
       </c>
       <c r="F18" t="n">
-        <v>7516887.29</v>
+        <v>305805.64</v>
       </c>
       <c r="G18" t="n">
-        <v>6813631.04</v>
+        <v>288797.79</v>
       </c>
       <c r="H18" t="n">
-        <v>55347.98</v>
+        <v>27672.53</v>
       </c>
       <c r="I18" t="n">
-        <v>249487.78</v>
-      </c>
-      <c r="J18" t="n">
-        <v>304835.76</v>
+        <v>26155.45</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1014,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>533594583.23</v>
+        <v>1391009.5</v>
       </c>
       <c r="F19" t="n">
-        <v>523602791.54</v>
+        <v>1160307.99</v>
       </c>
       <c r="G19" t="n">
-        <v>524266165.17</v>
+        <v>1002913.14</v>
       </c>
       <c r="H19" t="n">
-        <v>46197437.79</v>
+        <v>265290.28</v>
       </c>
       <c r="I19" t="n">
-        <v>5632677.28</v>
-      </c>
-      <c r="J19" t="n">
-        <v>51830115.07</v>
+        <v>304835.76</v>
       </c>
     </row>
     <row r="20">
@@ -1116,34 +1047,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>61200638.61</v>
+        <v>23875233.05</v>
       </c>
       <c r="F20" t="n">
-        <v>58218035.71</v>
+        <v>22617628.91</v>
       </c>
       <c r="G20" t="n">
-        <v>55031527.64</v>
+        <v>20290378.83</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5673896.25</v>
       </c>
       <c r="I20" t="n">
-        <v>1781014.41</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1781014.41</v>
+        <v>51830115.07</v>
       </c>
     </row>
     <row r="21">
@@ -1152,34 +1080,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1041559.94</v>
+        <v>13200301.49</v>
       </c>
       <c r="F21" t="n">
-        <v>823642.04</v>
+        <v>10601805.3</v>
       </c>
       <c r="G21" t="n">
-        <v>813093.72</v>
+        <v>9355457.49</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1819078.93</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
+        <v>1781014.41</v>
       </c>
     </row>
     <row r="22">
@@ -1188,34 +1113,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>63780232.72</v>
+        <v>1041550.11</v>
       </c>
       <c r="F22" t="n">
-        <v>61454087.81</v>
+        <v>823632.21</v>
       </c>
       <c r="G22" t="n">
-        <v>60658393.88</v>
+        <v>813083.89</v>
       </c>
       <c r="H22" t="n">
-        <v>203832.51</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3314473.99</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3518306.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1224,34 +1146,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>191504888.5</v>
+        <v>8711865.439999999</v>
       </c>
       <c r="F23" t="n">
-        <v>184497317.71</v>
+        <v>6481416.14</v>
       </c>
       <c r="G23" t="n">
-        <v>182485356.67</v>
+        <v>5764193.26</v>
       </c>
       <c r="H23" t="n">
-        <v>811297.6</v>
+        <v>3353522.33</v>
       </c>
       <c r="I23" t="n">
-        <v>3954289.12</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4765586.72</v>
+        <v>3518306.5</v>
       </c>
     </row>
     <row r="24">
@@ -1260,34 +1179,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5173333.28</v>
+        <v>8183389.62</v>
       </c>
       <c r="F24" t="n">
-        <v>5153333.28</v>
+        <v>6553677.43</v>
       </c>
       <c r="G24" t="n">
-        <v>3822182.56</v>
+        <v>5394613.91</v>
       </c>
       <c r="H24" t="n">
-        <v>50000</v>
+        <v>4049523.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>50000</v>
+        <v>4765586.72</v>
       </c>
     </row>
     <row r="25">
@@ -1296,34 +1212,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>17635213.7</v>
-      </c>
-      <c r="F25" t="n">
-        <v>17616149.93</v>
-      </c>
-      <c r="G25" t="n">
-        <v>16185012.28</v>
-      </c>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>130211.04</v>
-      </c>
-      <c r="J25" t="n">
-        <v>130211.04</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="26">
@@ -1332,34 +1239,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>5060964</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1670773.97</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1595111.21</v>
-      </c>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>202000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
+        <v>130211.04</v>
       </c>
     </row>
     <row r="27">
@@ -1368,34 +1266,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14312560.43</v>
+        <v>4925964</v>
       </c>
       <c r="F27" t="n">
-        <v>8943123.68</v>
+        <v>1535773.97</v>
       </c>
       <c r="G27" t="n">
-        <v>8217694.4</v>
+        <v>1460111.21</v>
       </c>
       <c r="H27" t="n">
-        <v>219306.4</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>11388620.84</v>
-      </c>
-      <c r="J27" t="n">
-        <v>11607927.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1404,34 +1299,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FEPJ</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4031</v>
+        <v>4451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2274700897.5</v>
+        <v>11546671.43</v>
       </c>
       <c r="F28" t="n">
-        <v>1956354064.55</v>
+        <v>6450291.06</v>
       </c>
       <c r="G28" t="n">
-        <v>1765456359.42</v>
+        <v>5715303.13</v>
       </c>
       <c r="H28" t="n">
-        <v>5636386.57</v>
+        <v>11657758.81</v>
       </c>
       <c r="I28" t="n">
-        <v>162851696.69</v>
-      </c>
-      <c r="J28" t="n">
-        <v>168488083.26</v>
+        <v>11607927.24</v>
       </c>
     </row>
     <row r="29">
@@ -1440,34 +1332,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>11829504614.64</v>
+        <v>1755044715.54</v>
       </c>
       <c r="F29" t="n">
-        <v>11406407458.04</v>
+        <v>1462515231.03</v>
       </c>
       <c r="G29" t="n">
-        <v>11283113714.34</v>
+        <v>1276681604.61</v>
       </c>
       <c r="H29" t="n">
-        <v>863891921.1</v>
+        <v>183432578.66</v>
       </c>
       <c r="I29" t="n">
-        <v>625577799.01</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1489469720.11</v>
+        <v>168488083.26</v>
       </c>
     </row>
     <row r="30">
@@ -1476,34 +1365,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4691</v>
+        <v>4291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49389640.21</v>
+        <v>1255009190.95</v>
       </c>
       <c r="F30" t="n">
-        <v>15901164.57</v>
+        <v>971143688.66</v>
       </c>
       <c r="G30" t="n">
-        <v>13533037.66</v>
+        <v>878763047.29</v>
       </c>
       <c r="H30" t="n">
-        <v>1152378.09</v>
+        <v>917554227.8099999</v>
       </c>
       <c r="I30" t="n">
-        <v>44348538.92</v>
-      </c>
-      <c r="J30" t="n">
-        <v>45500917.01</v>
+        <v>1489469720.11</v>
       </c>
     </row>
     <row r="31">
@@ -1512,34 +1398,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4701</v>
+        <v>4691</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1242375.3</v>
+        <v>49151714.29</v>
       </c>
       <c r="F31" t="n">
-        <v>921616.21</v>
+        <v>15663238.65</v>
       </c>
       <c r="G31" t="n">
-        <v>921884.45</v>
+        <v>13295111.74</v>
       </c>
       <c r="H31" t="n">
-        <v>4275.66</v>
+        <v>44970002.44</v>
       </c>
       <c r="I31" t="n">
-        <v>446306.33</v>
-      </c>
-      <c r="J31" t="n">
-        <v>450581.99</v>
+        <v>45500917.01</v>
       </c>
     </row>
     <row r="32">
@@ -1548,34 +1431,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4711</v>
+        <v>4701</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>17508957839.76</v>
+        <v>355297.17</v>
       </c>
       <c r="F32" t="n">
-        <v>17468843822.73</v>
+        <v>34538.08</v>
       </c>
       <c r="G32" t="n">
-        <v>17473304282.39</v>
+        <v>33211.68</v>
       </c>
       <c r="H32" t="n">
-        <v>11281.2</v>
+        <v>446339.6</v>
       </c>
       <c r="I32" t="n">
-        <v>754605.42</v>
-      </c>
-      <c r="J32" t="n">
-        <v>765886.62</v>
+        <v>450581.99</v>
       </c>
     </row>
     <row r="33">
@@ -1584,34 +1464,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2151</v>
+        <v>4711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>88180552.39</v>
-      </c>
-      <c r="F33" t="n">
-        <v>80251235.98</v>
-      </c>
-      <c r="G33" t="n">
-        <v>78333556.76000001</v>
-      </c>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>16912.22</v>
+        <v>819706.92</v>
       </c>
       <c r="I33" t="n">
-        <v>1852521.82</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1869434.04</v>
+        <v>765886.62</v>
       </c>
     </row>
     <row r="34">
@@ -1620,34 +1491,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2271</v>
+        <v>2151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2332862602.72</v>
+        <v>39930371.39</v>
       </c>
       <c r="F34" t="n">
-        <v>2250096399.41</v>
+        <v>32059613.35</v>
       </c>
       <c r="G34" t="n">
-        <v>2191298111.28</v>
+        <v>30159058.43</v>
       </c>
       <c r="H34" t="n">
-        <v>8172915.53</v>
+        <v>1925197.82</v>
       </c>
       <c r="I34" t="n">
-        <v>83039239.16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>91212154.69</v>
+        <v>1869434.04</v>
       </c>
     </row>
     <row r="35">
@@ -1656,34 +1524,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4341</v>
+        <v>2271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4415220.16</v>
+        <v>637251169.62</v>
       </c>
       <c r="F35" t="n">
-        <v>3506542.63</v>
+        <v>562460506.39</v>
       </c>
       <c r="G35" t="n">
-        <v>2790383.33</v>
+        <v>509824656.41</v>
       </c>
       <c r="H35" t="n">
-        <v>183731.44</v>
+        <v>85403649.95999999</v>
       </c>
       <c r="I35" t="n">
-        <v>384241.87</v>
-      </c>
-      <c r="J35" t="n">
-        <v>567973.3100000001</v>
+        <v>91212154.69</v>
       </c>
     </row>
     <row r="36">
@@ -1692,34 +1557,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4091</v>
+        <v>4341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4781856.89</v>
+        <v>1238646.3</v>
       </c>
       <c r="F36" t="n">
-        <v>1781856.89</v>
+        <v>947330.39</v>
       </c>
       <c r="G36" t="n">
-        <v>1780610.81</v>
+        <v>780252.97</v>
       </c>
       <c r="H36" t="n">
-        <v>1860786.86</v>
+        <v>493625.93</v>
       </c>
       <c r="I36" t="n">
-        <v>931646.02</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2792432.88</v>
+        <v>567973.3100000001</v>
       </c>
     </row>
     <row r="37">
@@ -1728,34 +1590,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2061</v>
+        <v>4091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>69147295.90000001</v>
+        <v>3035200</v>
       </c>
       <c r="F37" t="n">
-        <v>66097932.41</v>
+        <v>35200</v>
       </c>
       <c r="G37" t="n">
-        <v>64809217.45</v>
+        <v>33953.92</v>
       </c>
       <c r="H37" t="n">
-        <v>10992.51</v>
+        <v>960347.88</v>
       </c>
       <c r="I37" t="n">
-        <v>2944724.82</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2955717.33</v>
+        <v>2792432.88</v>
       </c>
     </row>
     <row r="38">
@@ -1764,34 +1623,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4141</v>
+        <v>2061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32022766.9</v>
+        <v>12757331.86</v>
       </c>
       <c r="F38" t="n">
-        <v>22913023.72</v>
+        <v>9740265.92</v>
       </c>
       <c r="G38" t="n">
-        <v>22137652.86</v>
+        <v>8521525.460000001</v>
       </c>
       <c r="H38" t="n">
-        <v>669506.88</v>
+        <v>3018901.62</v>
       </c>
       <c r="I38" t="n">
-        <v>4513043.66</v>
-      </c>
-      <c r="J38" t="n">
-        <v>5182550.54</v>
+        <v>2955717.33</v>
       </c>
     </row>
     <row r="39">
@@ -1800,34 +1656,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4631</v>
+        <v>4141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>497939201.43</v>
+        <v>32022766.9</v>
       </c>
       <c r="F39" t="n">
-        <v>379996046.23</v>
+        <v>22913023.72</v>
       </c>
       <c r="G39" t="n">
-        <v>356001665.76</v>
+        <v>22137652.86</v>
       </c>
       <c r="H39" t="n">
-        <v>6144215.84</v>
+        <v>4845340.62</v>
       </c>
       <c r="I39" t="n">
-        <v>223775960.7</v>
-      </c>
-      <c r="J39" t="n">
-        <v>229920176.54</v>
+        <v>5182550.54</v>
       </c>
     </row>
     <row r="40">
@@ -1836,34 +1689,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8462182.16</v>
+        <v>451082505.08</v>
       </c>
       <c r="F40" t="n">
-        <v>7716382.45</v>
+        <v>333139349.88</v>
       </c>
       <c r="G40" t="n">
-        <v>7622126.71</v>
+        <v>309471696.47</v>
       </c>
       <c r="H40" t="n">
-        <v>256168.61</v>
+        <v>228871575.25</v>
       </c>
       <c r="I40" t="n">
-        <v>287975.89</v>
-      </c>
-      <c r="J40" t="n">
-        <v>544144.5</v>
+        <v>229920176.54</v>
       </c>
     </row>
     <row r="41">
@@ -1872,34 +1722,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>239438177.07</v>
+        <v>2195965.81</v>
       </c>
       <c r="F41" t="n">
-        <v>238618171.81</v>
+        <v>1531546.83</v>
       </c>
       <c r="G41" t="n">
-        <v>238609881.4</v>
+        <v>1457719.77</v>
       </c>
       <c r="H41" t="n">
-        <v>9732.950000000001</v>
+        <v>294535.78</v>
       </c>
       <c r="I41" t="n">
-        <v>1418075.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1427808.25</v>
+        <v>544144.5</v>
       </c>
     </row>
     <row r="42">
@@ -1908,34 +1755,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FUNDHAB</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4121</v>
+        <v>4551</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>9244101.68</v>
-      </c>
-      <c r="F42" t="n">
-        <v>8478581.68</v>
-      </c>
-      <c r="G42" t="n">
-        <v>7748031.86</v>
-      </c>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1418075.3</v>
       </c>
       <c r="I42" t="n">
-        <v>893205</v>
-      </c>
-      <c r="J42" t="n">
-        <v>893205</v>
+        <v>1427808.25</v>
       </c>
     </row>
     <row r="43">
@@ -1944,29 +1782,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FUNDIF</t>
+          <t>FUNDHAB</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4421</v>
+        <v>4121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>490000</v>
-      </c>
-      <c r="F43" t="n">
-        <v>470895.13</v>
-      </c>
-      <c r="G43" t="n">
-        <v>470000</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>970875</v>
+      </c>
+      <c r="I43" t="n">
+        <v>893205</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1974,35 +1809,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2261</v>
+        <v>4421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>617079458.6900001</v>
+        <v>20000</v>
       </c>
       <c r="F44" t="n">
-        <v>457880133.86</v>
+        <v>895.13</v>
       </c>
       <c r="G44" t="n">
-        <v>414275548.19</v>
-      </c>
-      <c r="H44" t="n">
-        <v>915067.75</v>
-      </c>
-      <c r="I44" t="n">
-        <v>52633604.13</v>
-      </c>
-      <c r="J44" t="n">
-        <v>53548671.88</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2010,34 +1838,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FUNEMP</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4441</v>
+        <v>2261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21754563.35</v>
+        <v>495523719.04</v>
       </c>
       <c r="F45" t="n">
-        <v>12547861.55</v>
+        <v>337261696.37</v>
       </c>
       <c r="G45" t="n">
-        <v>12146604.86</v>
+        <v>293894526.77</v>
       </c>
       <c r="H45" t="n">
-        <v>69519.91</v>
+        <v>53506720.61</v>
       </c>
       <c r="I45" t="n">
-        <v>17013291.39</v>
-      </c>
-      <c r="J45" t="n">
-        <v>17082811.3</v>
+        <v>53548671.88</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +1871,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4381</v>
+        <v>4441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>121090271.58</v>
+        <v>7637174.13</v>
       </c>
       <c r="F46" t="n">
-        <v>82874506.28</v>
+        <v>2797180.54</v>
       </c>
       <c r="G46" t="n">
-        <v>79003714.81</v>
+        <v>2711601.55</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>17513977.46</v>
       </c>
       <c r="I46" t="n">
-        <v>12075855.48</v>
-      </c>
-      <c r="J46" t="n">
-        <v>12075855.48</v>
+        <v>17082811.3</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +1904,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1071</v>
+        <v>4381</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>39892772.32</v>
+        <v>121090271.58</v>
       </c>
       <c r="F47" t="n">
-        <v>35166360.52</v>
+        <v>82874506.28</v>
       </c>
       <c r="G47" t="n">
-        <v>34432753.31</v>
+        <v>79003714.81</v>
       </c>
       <c r="H47" t="n">
-        <v>630087.11</v>
+        <v>12762546.22</v>
       </c>
       <c r="I47" t="n">
-        <v>7450507.6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>8080594.71</v>
+        <v>12075855.48</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +1937,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1916</v>
+        <v>1071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3797673691.69</v>
+        <v>24306544.17</v>
       </c>
       <c r="F48" t="n">
-        <v>3797673691.69</v>
+        <v>19596748.3</v>
       </c>
       <c r="G48" t="n">
-        <v>3525271258.01</v>
+        <v>18628488.51</v>
       </c>
       <c r="H48" t="n">
-        <v>158424713.64</v>
+        <v>7552138.54</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>158424713.64</v>
+        <v>8080594.71</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +1970,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2321</v>
+        <v>1916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>393216438.36</v>
-      </c>
-      <c r="F49" t="n">
-        <v>350212418.49</v>
-      </c>
-      <c r="G49" t="n">
-        <v>340044994.95</v>
-      </c>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1352290.48</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>28148241.67</v>
-      </c>
-      <c r="J49" t="n">
-        <v>29500532.15</v>
+        <v>158424713.64</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +1997,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2421</v>
+        <v>2321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53824647.21</v>
+        <v>194553389.21</v>
       </c>
       <c r="F50" t="n">
-        <v>33871287.27</v>
+        <v>152315629.76</v>
       </c>
       <c r="G50" t="n">
-        <v>32392034.26</v>
+        <v>142430456.67</v>
       </c>
       <c r="H50" t="n">
-        <v>656114.84</v>
+        <v>28663837.09</v>
       </c>
       <c r="I50" t="n">
-        <v>7875523.48</v>
-      </c>
-      <c r="J50" t="n">
-        <v>8531638.32</v>
+        <v>29500532.15</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2030,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2101</v>
+        <v>2421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>217344980.62</v>
+        <v>38177306.08</v>
       </c>
       <c r="F51" t="n">
-        <v>207079100.46</v>
+        <v>18482671.42</v>
       </c>
       <c r="G51" t="n">
-        <v>198091936.58</v>
+        <v>17004241.95</v>
       </c>
       <c r="H51" t="n">
-        <v>521685.56</v>
+        <v>7988900.77</v>
       </c>
       <c r="I51" t="n">
-        <v>4299011.63</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4820697.19</v>
+        <v>8531638.32</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2063,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32151361.8</v>
+        <v>65495205.41</v>
       </c>
       <c r="F52" t="n">
-        <v>29851278.47</v>
+        <v>55936692.22</v>
       </c>
       <c r="G52" t="n">
-        <v>27723914.95</v>
+        <v>47535803.18</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1</v>
+        <v>4470595.78</v>
       </c>
       <c r="I52" t="n">
-        <v>1740955.49</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1740955.59</v>
+        <v>4820697.19</v>
       </c>
     </row>
     <row r="53">
@@ -2298,34 +2096,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2241</v>
+        <v>2201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>163783014.55</v>
+        <v>9708187.99</v>
       </c>
       <c r="F53" t="n">
-        <v>159345489.81</v>
+        <v>7604913.34</v>
       </c>
       <c r="G53" t="n">
-        <v>158705842.44</v>
+        <v>6876465.82</v>
       </c>
       <c r="H53" t="n">
-        <v>28637714.75</v>
+        <v>1768674.95</v>
       </c>
       <c r="I53" t="n">
-        <v>1953947.48</v>
-      </c>
-      <c r="J53" t="n">
-        <v>30591662.23</v>
+        <v>1740955.59</v>
       </c>
     </row>
     <row r="54">
@@ -2334,34 +2129,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2371</v>
+        <v>2241</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>281022284.81</v>
+        <v>14650161.45</v>
       </c>
       <c r="F54" t="n">
-        <v>272651863.28</v>
+        <v>11420102.49</v>
       </c>
       <c r="G54" t="n">
-        <v>271364090.09</v>
+        <v>10897819.71</v>
       </c>
       <c r="H54" t="n">
-        <v>21502.46</v>
+        <v>2002616.88</v>
       </c>
       <c r="I54" t="n">
-        <v>3360355.35</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3381857.81</v>
+        <v>30591662.23</v>
       </c>
     </row>
     <row r="55">
@@ -2370,34 +2162,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2331</v>
+        <v>2371</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>33811040.59</v>
+        <v>22693046.41</v>
       </c>
       <c r="F55" t="n">
-        <v>33218643.65</v>
+        <v>14620527.35</v>
       </c>
       <c r="G55" t="n">
-        <v>31654005.09</v>
+        <v>13036414.46</v>
       </c>
       <c r="H55" t="n">
-        <v>519444.53</v>
+        <v>3501968.2</v>
       </c>
       <c r="I55" t="n">
-        <v>471410.62</v>
-      </c>
-      <c r="J55" t="n">
-        <v>990855.15</v>
+        <v>3381857.81</v>
       </c>
     </row>
     <row r="56">
@@ -2406,29 +2195,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IPLEMG</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2361</v>
+        <v>2331</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>66040115.72</v>
+        <v>11671345.01</v>
       </c>
       <c r="F56" t="n">
-        <v>66040115.72</v>
+        <v>11086934.99</v>
       </c>
       <c r="G56" t="n">
-        <v>66040115.72</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+        <v>9408581.539999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>485486.11</v>
+      </c>
+      <c r="I56" t="n">
+        <v>990855.15</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2436,35 +2228,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2011</v>
+        <v>2361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1725474955.8</v>
+        <v>66040115.72</v>
       </c>
       <c r="F57" t="n">
-        <v>1598962422.88</v>
+        <v>66040115.72</v>
       </c>
       <c r="G57" t="n">
-        <v>1555299505.74</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1217572.7</v>
-      </c>
-      <c r="I57" t="n">
-        <v>166587616.35</v>
-      </c>
-      <c r="J57" t="n">
-        <v>167805189.05</v>
-      </c>
+        <v>66040115.72</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2472,34 +2257,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2121</v>
+        <v>2011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3010650321.59</v>
+        <v>264889228.82</v>
       </c>
       <c r="F58" t="n">
-        <v>2990182081.12</v>
+        <v>214463709.92</v>
       </c>
       <c r="G58" t="n">
-        <v>2961013745.75</v>
+        <v>198217479.99</v>
       </c>
       <c r="H58" t="n">
-        <v>70175211.91</v>
+        <v>170636228.2</v>
       </c>
       <c r="I58" t="n">
-        <v>12134894.13</v>
-      </c>
-      <c r="J58" t="n">
-        <v>82310106.04000001</v>
+        <v>167805189.05</v>
       </c>
     </row>
     <row r="59">
@@ -2508,34 +2290,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>34101030</v>
+        <v>94198750.20999999</v>
       </c>
       <c r="F59" t="n">
-        <v>32049801.81</v>
+        <v>85490003.17</v>
       </c>
       <c r="G59" t="n">
-        <v>31364550.07</v>
+        <v>78650414.76000001</v>
       </c>
       <c r="H59" t="n">
-        <v>99361.64999999999</v>
+        <v>14877537.3</v>
       </c>
       <c r="I59" t="n">
-        <v>974721.99</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1074083.64</v>
+        <v>82310106.04000001</v>
       </c>
     </row>
     <row r="60">
@@ -2544,34 +2323,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2041</v>
+        <v>2251</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2753285.11</v>
+        <v>11748636.33</v>
       </c>
       <c r="F60" t="n">
-        <v>2718960.43</v>
+        <v>9795460.77</v>
       </c>
       <c r="G60" t="n">
-        <v>2712294.25</v>
+        <v>9135232.35</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1032352.18</v>
       </c>
       <c r="I60" t="n">
-        <v>52615.45</v>
-      </c>
-      <c r="J60" t="n">
-        <v>52615.45</v>
+        <v>1074083.64</v>
       </c>
     </row>
     <row r="61">
@@ -2580,34 +2356,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1101</v>
+        <v>2041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>16775084.75</v>
+        <v>271814.15</v>
       </c>
       <c r="F61" t="n">
-        <v>16686029.56</v>
+        <v>237489.47</v>
       </c>
       <c r="G61" t="n">
-        <v>16501107.08</v>
+        <v>229568.35</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>53618.61</v>
       </c>
       <c r="I61" t="n">
-        <v>35612.89</v>
-      </c>
-      <c r="J61" t="n">
-        <v>35612.89</v>
+        <v>52615.45</v>
       </c>
     </row>
     <row r="62">
@@ -2616,34 +2389,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>MG INVESTE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1915</v>
+        <v>4621</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>77370454.08</v>
-      </c>
-      <c r="F62" t="n">
-        <v>77346508.56999999</v>
-      </c>
-      <c r="G62" t="n">
-        <v>77346508.56999999</v>
-      </c>
+          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>259334068.7</v>
-      </c>
-      <c r="J62" t="n">
-        <v>259334068.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2652,34 +2416,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1511</v>
+        <v>1101</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2971107807.85</v>
+        <v>2046980.74</v>
       </c>
       <c r="F63" t="n">
-        <v>2911787285.47</v>
+        <v>1957925.55</v>
       </c>
       <c r="G63" t="n">
-        <v>2882948197.58</v>
+        <v>1772661.97</v>
       </c>
       <c r="H63" t="n">
-        <v>6144267.39</v>
+        <v>37893.74</v>
       </c>
       <c r="I63" t="n">
-        <v>64134975.09</v>
-      </c>
-      <c r="J63" t="n">
-        <v>70279242.48</v>
+        <v>35612.89</v>
       </c>
     </row>
     <row r="64">
@@ -2688,34 +2449,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PGJ</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1091</v>
+        <v>1915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTICA</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>3719366289.78</v>
-      </c>
-      <c r="F64" t="n">
-        <v>3595457252.17</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3560537239.55</v>
-      </c>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>2972698.61</v>
+        <v>259334068.7</v>
       </c>
       <c r="I64" t="n">
-        <v>67746170.34</v>
-      </c>
-      <c r="J64" t="n">
-        <v>70718868.95</v>
+        <v>259334068.7</v>
       </c>
     </row>
     <row r="65">
@@ -2724,34 +2476,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1251</v>
+        <v>1511</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>14358949915.03</v>
+        <v>267315279.2</v>
       </c>
       <c r="F65" t="n">
-        <v>14172994593.1</v>
+        <v>208634145.04</v>
       </c>
       <c r="G65" t="n">
-        <v>14136708514.63</v>
+        <v>180005398.91</v>
       </c>
       <c r="H65" t="n">
-        <v>25047110.83</v>
+        <v>66121789.56</v>
       </c>
       <c r="I65" t="n">
-        <v>200233686.02</v>
-      </c>
-      <c r="J65" t="n">
-        <v>225280796.85</v>
+        <v>70279242.48</v>
       </c>
     </row>
     <row r="66">
@@ -2760,34 +2509,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1721</v>
+        <v>1091</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>11376822.58</v>
+        <v>361768591.97</v>
       </c>
       <c r="F66" t="n">
-        <v>10825343.53</v>
+        <v>249189937.94</v>
       </c>
       <c r="G66" t="n">
-        <v>10646102.96</v>
+        <v>213360348.97</v>
       </c>
       <c r="H66" t="n">
-        <v>256630.64</v>
+        <v>75426918.81999999</v>
       </c>
       <c r="I66" t="n">
-        <v>226579.48</v>
-      </c>
-      <c r="J66" t="n">
-        <v>483210.12</v>
+        <v>70718868.95</v>
       </c>
     </row>
     <row r="67">
@@ -2796,34 +2542,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>144310208.36</v>
+        <v>536836197.52</v>
       </c>
       <c r="F67" t="n">
-        <v>121768607.78</v>
+        <v>353871358.66</v>
       </c>
       <c r="G67" t="n">
-        <v>115667927.76</v>
+        <v>317606917.36</v>
       </c>
       <c r="H67" t="n">
-        <v>16655601.21</v>
+        <v>206917850.11</v>
       </c>
       <c r="I67" t="n">
-        <v>13370006.41</v>
-      </c>
-      <c r="J67" t="n">
-        <v>30025607.62</v>
+        <v>225280796.85</v>
       </c>
     </row>
     <row r="68">
@@ -2832,34 +2575,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1631</v>
+        <v>1721</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>9422516.710000001</v>
+        <v>2350061.46</v>
       </c>
       <c r="F68" t="n">
-        <v>9269804.6</v>
+        <v>1892195.94</v>
       </c>
       <c r="G68" t="n">
-        <v>9157892.960000001</v>
+        <v>1689717.16</v>
       </c>
       <c r="H68" t="n">
-        <v>7873.12</v>
+        <v>230141.9</v>
       </c>
       <c r="I68" t="n">
-        <v>3228098.93</v>
-      </c>
-      <c r="J68" t="n">
-        <v>3235972.05</v>
+        <v>483210.12</v>
       </c>
     </row>
     <row r="69">
@@ -2868,34 +2608,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1711</v>
+        <v>1231</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>145415971.84</v>
+        <v>46052711.07</v>
       </c>
       <c r="F69" t="n">
-        <v>57212986.34</v>
+        <v>24033724.92</v>
       </c>
       <c r="G69" t="n">
-        <v>54811118.27</v>
+        <v>22352988.79</v>
       </c>
       <c r="H69" t="n">
-        <v>13711.91</v>
+        <v>13999924.75</v>
       </c>
       <c r="I69" t="n">
-        <v>45385504.04</v>
-      </c>
-      <c r="J69" t="n">
-        <v>45399215.95</v>
+        <v>30025607.62</v>
       </c>
     </row>
     <row r="70">
@@ -2904,34 +2641,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1271</v>
+        <v>1631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>278574229.65</v>
+        <v>852321.76</v>
       </c>
       <c r="F70" t="n">
-        <v>275244209.69</v>
+        <v>787077.5699999999</v>
       </c>
       <c r="G70" t="n">
-        <v>272306597.26</v>
+        <v>667275.58</v>
       </c>
       <c r="H70" t="n">
-        <v>2848477.47</v>
+        <v>3335236.84</v>
       </c>
       <c r="I70" t="n">
-        <v>1058475.57</v>
-      </c>
-      <c r="J70" t="n">
-        <v>3906953.04</v>
+        <v>3235972.05</v>
       </c>
     </row>
     <row r="71">
@@ -2940,34 +2674,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1221</v>
+        <v>1711</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>73450042.36</v>
+        <v>132601486.52</v>
       </c>
       <c r="F71" t="n">
-        <v>68755382.68000001</v>
+        <v>44398501.02</v>
       </c>
       <c r="G71" t="n">
-        <v>67360741.43000001</v>
+        <v>41960496.94</v>
       </c>
       <c r="H71" t="n">
-        <v>20159858.67</v>
+        <v>47261689.65</v>
       </c>
       <c r="I71" t="n">
-        <v>2093275.95</v>
-      </c>
-      <c r="J71" t="n">
-        <v>22253134.62</v>
+        <v>45399215.95</v>
       </c>
     </row>
     <row r="72">
@@ -2976,34 +2707,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1481</v>
+        <v>1271</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>192351891.57</v>
+        <v>24020399.26</v>
       </c>
       <c r="F72" t="n">
-        <v>161820266.28</v>
+        <v>23055815.49</v>
       </c>
       <c r="G72" t="n">
-        <v>151442671.16</v>
+        <v>21290741.48</v>
       </c>
       <c r="H72" t="n">
-        <v>69047832.11</v>
+        <v>1217972.22</v>
       </c>
       <c r="I72" t="n">
-        <v>5228463.57</v>
-      </c>
-      <c r="J72" t="n">
-        <v>74276295.68000001</v>
+        <v>3906953.04</v>
       </c>
     </row>
     <row r="73">
@@ -3012,34 +2740,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>19265871510.98</v>
+        <v>15458773.97</v>
       </c>
       <c r="F73" t="n">
-        <v>18803285393.11</v>
+        <v>11698109.47</v>
       </c>
       <c r="G73" t="n">
-        <v>18714498875.1</v>
+        <v>10321899.57</v>
       </c>
       <c r="H73" t="n">
-        <v>270741595.99</v>
+        <v>3323938.06</v>
       </c>
       <c r="I73" t="n">
-        <v>353672915.64</v>
-      </c>
-      <c r="J73" t="n">
-        <v>624414511.63</v>
+        <v>22253134.62</v>
       </c>
     </row>
     <row r="74">
@@ -3048,34 +2773,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1191</v>
+        <v>1481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1774005537.77</v>
+        <v>45799626.97</v>
       </c>
       <c r="F74" t="n">
-        <v>1675743095.87</v>
+        <v>19663330.79</v>
       </c>
       <c r="G74" t="n">
-        <v>1655219211.46</v>
+        <v>17661206.98</v>
       </c>
       <c r="H74" t="n">
-        <v>9452783.43</v>
+        <v>5483592.66</v>
       </c>
       <c r="I74" t="n">
-        <v>44016084.48</v>
-      </c>
-      <c r="J74" t="n">
-        <v>53468867.91</v>
+        <v>74276295.68000001</v>
       </c>
     </row>
     <row r="75">
@@ -3084,34 +2806,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1491</v>
+        <v>1261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>936918721.67</v>
+        <v>1125271888.87</v>
       </c>
       <c r="F75" t="n">
-        <v>903588865.71</v>
+        <v>904935712.55</v>
       </c>
       <c r="G75" t="n">
-        <v>899254287.64</v>
+        <v>866176085.0700001</v>
       </c>
       <c r="H75" t="n">
-        <v>2218245.96</v>
+        <v>367532161.71</v>
       </c>
       <c r="I75" t="n">
-        <v>40834360.64</v>
-      </c>
-      <c r="J75" t="n">
-        <v>43052606.6</v>
+        <v>624414511.63</v>
       </c>
     </row>
     <row r="76">
@@ -3120,34 +2839,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>739415330.3099999</v>
+        <v>252957628.78</v>
       </c>
       <c r="F76" t="n">
-        <v>535038118.5</v>
+        <v>166750977.01</v>
       </c>
       <c r="G76" t="n">
-        <v>520804921.24</v>
+        <v>149020387.35</v>
       </c>
       <c r="H76" t="n">
-        <v>79602772.47</v>
+        <v>46940993.5</v>
       </c>
       <c r="I76" t="n">
-        <v>79301096.69</v>
-      </c>
-      <c r="J76" t="n">
-        <v>158903869.16</v>
+        <v>53468867.91</v>
       </c>
     </row>
     <row r="77">
@@ -3156,34 +2872,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4151305223.12</v>
+        <v>39272457.81</v>
       </c>
       <c r="F77" t="n">
-        <v>4013226715.05</v>
+        <v>31577748.43</v>
       </c>
       <c r="G77" t="n">
-        <v>3984233963.53</v>
+        <v>28263386.76</v>
       </c>
       <c r="H77" t="n">
-        <v>16641871.41</v>
+        <v>41892385.89</v>
       </c>
       <c r="I77" t="n">
-        <v>126747618.81</v>
-      </c>
-      <c r="J77" t="n">
-        <v>143389490.22</v>
+        <v>43052606.6</v>
       </c>
     </row>
     <row r="78">
@@ -3192,34 +2905,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>184730264.23</v>
+        <v>133190758</v>
       </c>
       <c r="F78" t="n">
-        <v>174620059.85</v>
+        <v>64082056.37</v>
       </c>
       <c r="G78" t="n">
-        <v>171768182.39</v>
+        <v>59285890.55</v>
       </c>
       <c r="H78" t="n">
-        <v>16148951.81</v>
+        <v>80712746.70999999</v>
       </c>
       <c r="I78" t="n">
-        <v>3698488.6</v>
-      </c>
-      <c r="J78" t="n">
-        <v>19847440.41</v>
+        <v>158903869.16</v>
       </c>
     </row>
     <row r="79">
@@ -3228,34 +2938,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>855546794.0599999</v>
+        <v>721023034.88</v>
       </c>
       <c r="F79" t="n">
-        <v>760671962.17</v>
+        <v>596515406.21</v>
       </c>
       <c r="G79" t="n">
-        <v>719982759.6799999</v>
+        <v>571863770.89</v>
       </c>
       <c r="H79" t="n">
-        <v>10865754.29</v>
+        <v>131416434.6</v>
       </c>
       <c r="I79" t="n">
-        <v>34522196.21</v>
-      </c>
-      <c r="J79" t="n">
-        <v>45387950.5</v>
+        <v>143389490.22</v>
       </c>
     </row>
     <row r="80">
@@ -3264,34 +2971,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TCEMG</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1021</v>
+        <v>1371</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1210662331.77</v>
+        <v>36419261.4</v>
       </c>
       <c r="F80" t="n">
-        <v>1176050058.41</v>
+        <v>28445163.15</v>
       </c>
       <c r="G80" t="n">
-        <v>1162004344.71</v>
+        <v>25750735.68</v>
       </c>
       <c r="H80" t="n">
-        <v>181476.44</v>
+        <v>3974388.51</v>
       </c>
       <c r="I80" t="n">
-        <v>15555853.23</v>
-      </c>
-      <c r="J80" t="n">
-        <v>15737329.67</v>
+        <v>19847440.41</v>
       </c>
     </row>
     <row r="81">
@@ -3300,29 +3004,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TJMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1031</v>
+        <v>1501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>9337455728.58</v>
+        <v>426089339.77</v>
       </c>
       <c r="F81" t="n">
-        <v>9337455728.58</v>
+        <v>336251529.55</v>
       </c>
       <c r="G81" t="n">
-        <v>9337959841.530001</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+        <v>302054434.87</v>
+      </c>
+      <c r="H81" t="n">
+        <v>37507823.29</v>
+      </c>
+      <c r="I81" t="n">
+        <v>45387950.5</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3330,34 +3037,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TJMMG</t>
+          <t>TCEMG</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1051</v>
+        <v>1021</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>136130325.04</v>
+        <v>132823979.43</v>
       </c>
       <c r="F82" t="n">
-        <v>130482064.44</v>
+        <v>99260249.26000001</v>
       </c>
       <c r="G82" t="n">
-        <v>129211193.82</v>
+        <v>83759721.16</v>
       </c>
       <c r="H82" t="n">
-        <v>191463.61</v>
+        <v>17249916.35</v>
       </c>
       <c r="I82" t="n">
-        <v>3301434.56</v>
-      </c>
-      <c r="J82" t="n">
-        <v>3492898.17</v>
+        <v>15737329.67</v>
       </c>
     </row>
     <row r="83">
@@ -3366,34 +3070,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>TJMMG</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2211</v>
+        <v>1051</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>18099484.14</v>
+        <v>16200179.12</v>
       </c>
       <c r="F83" t="n">
-        <v>16714066.1</v>
+        <v>10600027.2</v>
       </c>
       <c r="G83" t="n">
-        <v>15905442.44</v>
+        <v>9342551.960000001</v>
       </c>
       <c r="H83" t="n">
-        <v>333380.82</v>
+        <v>3406783.22</v>
       </c>
       <c r="I83" t="n">
-        <v>636002.17</v>
-      </c>
-      <c r="J83" t="n">
-        <v>969382.99</v>
+        <v>3492898.17</v>
       </c>
     </row>
     <row r="84">
@@ -3402,34 +3103,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2351</v>
+        <v>2211</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>411019703.15</v>
+        <v>7215923.13</v>
       </c>
       <c r="F84" t="n">
-        <v>396207773.83</v>
+        <v>6003154.54</v>
       </c>
       <c r="G84" t="n">
-        <v>386312319.37</v>
+        <v>5287411.29</v>
       </c>
       <c r="H84" t="n">
-        <v>2944423.8</v>
+        <v>640162.9</v>
       </c>
       <c r="I84" t="n">
-        <v>10470000.42</v>
-      </c>
-      <c r="J84" t="n">
-        <v>13414424.22</v>
+        <v>969382.99</v>
       </c>
     </row>
     <row r="85">
@@ -3438,34 +3136,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>UEMG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2311</v>
+        <v>2351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>499332522.4</v>
+        <v>92828301.36</v>
       </c>
       <c r="F85" t="n">
-        <v>462442399.38</v>
+        <v>80633318.83</v>
       </c>
       <c r="G85" t="n">
-        <v>452206130.54</v>
+        <v>72014602.27</v>
       </c>
       <c r="H85" t="n">
-        <v>518698.7</v>
+        <v>10878129.05</v>
       </c>
       <c r="I85" t="n">
-        <v>37770634.5</v>
-      </c>
-      <c r="J85" t="n">
-        <v>38289333.2</v>
+        <v>13414424.22</v>
       </c>
     </row>
     <row r="86">
@@ -3474,33 +3169,63 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>91597823.66</v>
+      </c>
+      <c r="F86" t="n">
+        <v>59779051.56</v>
+      </c>
+      <c r="G86" t="n">
+        <v>53553271.07</v>
+      </c>
+      <c r="H86" t="n">
+        <v>41382813.33</v>
+      </c>
+      <c r="I86" t="n">
+        <v>38289333.2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C87" t="n">
         <v>2281</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E86" t="n">
-        <v>6571067.71</v>
-      </c>
-      <c r="F86" t="n">
-        <v>6006116.69</v>
-      </c>
-      <c r="G86" t="n">
-        <v>5621531.59</v>
-      </c>
-      <c r="H86" t="n">
-        <v>10063.62</v>
-      </c>
-      <c r="I86" t="n">
-        <v>209239.25</v>
-      </c>
-      <c r="J86" t="n">
+      <c r="E87" t="n">
+        <v>3474699.15</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2954558.38</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2609508.27</v>
+      </c>
+      <c r="H87" t="n">
+        <v>240590.47</v>
+      </c>
+      <c r="I87" t="n">
         <v>219302.87</v>
       </c>
     </row>
